--- a/Src/Assets/Common/Tables/Tables/Levels.xlsx
+++ b/Src/Assets/Common/Tables/Tables/Levels.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CCA\Src\Assets\Common\Tables\Tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CCA456\CCA\Src\Assets\Common\Tables\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE81BD3C-5567-4C63-90A2-1247E3538DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1E922F-D6FF-4667-A747-F171F036ACAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AI" sheetId="5" r:id="rId1"/>
@@ -18,20 +18,26 @@
     <sheet name="Character" sheetId="2" r:id="rId3"/>
     <sheet name="Emotion" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="548">
   <si>
     <t>Key</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1898,6 +1904,9 @@
   <si>
     <t>["double_bullet","double_sword","stab","cleave","laser_stab","laser_cleave","ghost_sever","spirit_sever","shoot","double_shoot","laser_shoot","laser_cannon","RPG","double_RPG","block","double_block","heavy_block","deflect","rebounce","counterblade","disarm","spectral_reflection","provoke","comeon"]</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlayerSkillSlots</t>
   </si>
 </sst>
 </file>
@@ -1965,7 +1974,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2002,8 +2011,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79995117038483843"/>
+        <bgColor theme="4" tint="0.79995117038483843"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79995117038483843"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79995117038483843"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -2035,11 +2074,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39994506668294322"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39994506668294322"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39994506668294322"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39994506668294322"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39994506668294322"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2059,7 +2122,7 @@
     <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2120,34 +2183,7 @@
     <xf numFmtId="9" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2167,6 +2203,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2449,19 +2503,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{259E49F2-2246-4E59-AF25-B4C5AD1F25A6}">
   <dimension ref="A1:M100"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="2" width="21.58203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.58203125" style="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.08203125" style="24" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.08203125" style="24" customWidth="1"/>
-    <col min="6" max="6" width="10.9140625" style="3" customWidth="1"/>
+    <col min="1" max="2" width="21.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5546875" style="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" style="24" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" style="24" customWidth="1"/>
+    <col min="6" max="6" width="10.88671875" style="3" customWidth="1"/>
     <col min="7" max="7" width="18.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="255.75" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.75" style="3"/>
+    <col min="8" max="8" width="255.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.77734375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -2492,20 +2546,20 @@
       <c r="L1" s="22"/>
       <c r="M1" s="22"/>
     </row>
-    <row r="2" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="23" t="s">
         <v>72</v>
       </c>
       <c r="B2" s="23" t="s">
         <v>281</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E2" s="32" t="b">
+      <c r="E2" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F2" s="1">
@@ -2523,7 +2577,7 @@
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
     </row>
-    <row r="3" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="24" t="s">
         <v>77</v>
       </c>
@@ -2536,20 +2590,20 @@
       <c r="D3" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="E3" s="37" t="b">
+      <c r="E3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F3" s="3">
         <v>2</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="G3" s="24" t="s">
         <v>241</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="6" t="s">
         <v>75</v>
       </c>
@@ -2559,10 +2613,10 @@
       <c r="C4" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E4" s="32" t="b">
+      <c r="E4" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F4" s="15">
@@ -2580,7 +2634,7 @@
       <c r="L4" s="15"/>
       <c r="M4" s="15"/>
     </row>
-    <row r="5" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
         <v>79</v>
       </c>
@@ -2593,33 +2647,33 @@
       <c r="D5" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="E5" s="37" t="b">
+      <c r="E5" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F5" s="3">
         <v>2</v>
       </c>
-      <c r="G5" s="31" t="s">
+      <c r="G5" s="24" t="s">
         <v>368</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="23" t="s">
         <v>81</v>
       </c>
       <c r="B6" s="23" t="s">
         <v>304</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E6" s="32" t="b">
+      <c r="E6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F6" s="15">
@@ -2628,7 +2682,7 @@
       <c r="G6" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H6" s="35" t="s">
+      <c r="H6" s="15" t="s">
         <v>460</v>
       </c>
       <c r="I6" s="15"/>
@@ -2637,7 +2691,7 @@
       <c r="L6" s="15"/>
       <c r="M6" s="15"/>
     </row>
-    <row r="7" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="3" t="s">
         <v>84</v>
       </c>
@@ -2650,33 +2704,33 @@
       <c r="D7" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="37" t="b">
+      <c r="E7" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F7" s="3">
         <v>3</v>
       </c>
-      <c r="G7" s="31" t="s">
+      <c r="G7" s="24" t="s">
         <v>241</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="23" t="s">
         <v>170</v>
       </c>
       <c r="B8" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="E8" s="32" t="b">
+      <c r="E8" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F8" s="15">
@@ -2694,7 +2748,7 @@
       <c r="L8" s="15"/>
       <c r="M8" s="15"/>
     </row>
-    <row r="9" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="3" t="s">
         <v>85</v>
       </c>
@@ -2707,20 +2761,20 @@
       <c r="D9" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="E9" s="37" t="b">
+      <c r="E9" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F9" s="3">
         <v>3</v>
       </c>
-      <c r="G9" s="31" t="s">
+      <c r="G9" s="24" t="s">
         <v>241</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="23" t="s">
         <v>87</v>
       </c>
@@ -2730,10 +2784,10 @@
       <c r="C10" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E10" s="32" t="b">
+      <c r="E10" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F10" s="15">
@@ -2751,7 +2805,7 @@
       <c r="L10" s="15"/>
       <c r="M10" s="15"/>
     </row>
-    <row r="11" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="3" t="s">
         <v>89</v>
       </c>
@@ -2764,33 +2818,33 @@
       <c r="D11" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="E11" s="37" t="b">
+      <c r="E11" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F11" s="3">
         <v>5</v>
       </c>
-      <c r="G11" s="31" t="s">
+      <c r="G11" s="24" t="s">
         <v>370</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="23" t="s">
         <v>91</v>
       </c>
       <c r="B12" s="23" t="s">
         <v>308</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E12" s="32" t="b">
+      <c r="E12" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F12" s="15">
@@ -2799,7 +2853,7 @@
       <c r="G12" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H12" s="35" t="s">
+      <c r="H12" s="15" t="s">
         <v>476</v>
       </c>
       <c r="I12" s="15"/>
@@ -2808,7 +2862,7 @@
       <c r="L12" s="15"/>
       <c r="M12" s="15"/>
     </row>
-    <row r="13" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="3" t="s">
         <v>309</v>
       </c>
@@ -2821,33 +2875,33 @@
       <c r="D13" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="E13" s="37" t="b">
+      <c r="E13" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F13" s="3">
         <v>4</v>
       </c>
-      <c r="G13" s="31" t="s">
+      <c r="G13" s="24" t="s">
         <v>372</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="6" t="s">
         <v>93</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E14" s="32" t="b">
+      <c r="E14" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F14" s="15">
@@ -2865,7 +2919,7 @@
       <c r="L14" s="15"/>
       <c r="M14" s="15"/>
     </row>
-    <row r="15" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="3" t="s">
         <v>169</v>
       </c>
@@ -2878,33 +2932,33 @@
       <c r="D15" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="E15" s="37" t="b">
+      <c r="E15" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F15" s="3">
         <v>3</v>
       </c>
-      <c r="G15" s="31" t="s">
+      <c r="G15" s="24" t="s">
         <v>241</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="6" t="s">
         <v>168</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E16" s="32" t="b">
+      <c r="E16" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F16" s="15">
@@ -2913,7 +2967,7 @@
       <c r="G16" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="H16" s="35" t="s">
+      <c r="H16" s="15" t="s">
         <v>413</v>
       </c>
       <c r="I16" s="15"/>
@@ -2922,7 +2976,7 @@
       <c r="L16" s="15"/>
       <c r="M16" s="15"/>
     </row>
-    <row r="17" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="3" t="s">
         <v>167</v>
       </c>
@@ -2935,33 +2989,33 @@
       <c r="D17" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="37" t="b">
+      <c r="E17" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F17" s="3">
         <v>9</v>
       </c>
-      <c r="G17" s="31" t="s">
+      <c r="G17" s="24" t="s">
         <v>371</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="23" t="s">
         <v>237</v>
       </c>
       <c r="B18" s="23" t="s">
         <v>237</v>
       </c>
-      <c r="C18" s="32" t="s">
+      <c r="C18" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="E18" s="32" t="b">
+      <c r="E18" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F18" s="15">
@@ -2979,7 +3033,7 @@
       <c r="L18" s="15"/>
       <c r="M18" s="15"/>
     </row>
-    <row r="19" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="3" t="s">
         <v>99</v>
       </c>
@@ -2992,33 +3046,33 @@
       <c r="D19" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="E19" s="37" t="b">
+      <c r="E19" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F19" s="3">
         <v>5</v>
       </c>
-      <c r="G19" s="31" t="s">
+      <c r="G19" s="24" t="s">
         <v>373</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="23" t="s">
         <v>100</v>
       </c>
       <c r="B20" s="23" t="s">
         <v>312</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E20" s="32" t="b">
+      <c r="E20" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F20" s="15">
@@ -3036,7 +3090,7 @@
       <c r="L20" s="15"/>
       <c r="M20" s="15"/>
     </row>
-    <row r="21" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="3" t="s">
         <v>457</v>
       </c>
@@ -3049,33 +3103,33 @@
       <c r="D21" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="E21" s="37" t="b">
+      <c r="E21" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F21" s="3">
         <v>4</v>
       </c>
-      <c r="G21" s="31" t="s">
+      <c r="G21" s="24" t="s">
         <v>374</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="23" t="s">
         <v>102</v>
       </c>
       <c r="B22" s="23" t="s">
         <v>314</v>
       </c>
-      <c r="C22" s="32" t="s">
+      <c r="C22" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="D22" s="32" t="s">
+      <c r="D22" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E22" s="32" t="b">
+      <c r="E22" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F22" s="15">
@@ -3093,7 +3147,7 @@
       <c r="L22" s="15"/>
       <c r="M22" s="15"/>
     </row>
-    <row r="23" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="3" t="s">
         <v>105</v>
       </c>
@@ -3106,33 +3160,33 @@
       <c r="D23" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="E23" s="37" t="b">
+      <c r="E23" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F23" s="3">
         <v>5</v>
       </c>
-      <c r="G23" s="31" t="s">
+      <c r="G23" s="24" t="s">
         <v>372</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="23" t="s">
         <v>107</v>
       </c>
       <c r="B24" s="23" t="s">
         <v>315</v>
       </c>
-      <c r="C24" s="32" t="s">
+      <c r="C24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D24" s="32" t="s">
+      <c r="D24" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E24" s="32" t="b">
+      <c r="E24" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F24" s="15">
@@ -3150,7 +3204,7 @@
       <c r="L24" s="15"/>
       <c r="M24" s="15"/>
     </row>
-    <row r="25" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="3" t="s">
         <v>458</v>
       </c>
@@ -3163,33 +3217,33 @@
       <c r="D25" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="E25" s="37" t="b">
+      <c r="E25" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F25" s="3">
         <v>2</v>
       </c>
-      <c r="G25" s="31" t="s">
+      <c r="G25" s="24" t="s">
         <v>377</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="23" t="s">
         <v>110</v>
       </c>
       <c r="B26" s="23" t="s">
         <v>319</v>
       </c>
-      <c r="C26" s="32" t="s">
+      <c r="C26" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="D26" s="32" t="s">
+      <c r="D26" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E26" s="32" t="b">
+      <c r="E26" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F26" s="15">
@@ -3207,7 +3261,7 @@
       <c r="L26" s="15"/>
       <c r="M26" s="15"/>
     </row>
-    <row r="27" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="3" t="s">
         <v>166</v>
       </c>
@@ -3220,33 +3274,33 @@
       <c r="D27" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="E27" s="37" t="b">
+      <c r="E27" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F27" s="3">
         <v>11</v>
       </c>
-      <c r="G27" s="31" t="s">
+      <c r="G27" s="24" t="s">
         <v>378</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="23" t="s">
         <v>112</v>
       </c>
       <c r="B28" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="C28" s="32" t="s">
+      <c r="C28" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="D28" s="32" t="s">
+      <c r="D28" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E28" s="32" t="b">
+      <c r="E28" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F28" s="15">
@@ -3255,7 +3309,7 @@
       <c r="G28" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="15" t="s">
         <v>413</v>
       </c>
       <c r="I28" s="15"/>
@@ -3264,7 +3318,7 @@
       <c r="L28" s="15"/>
       <c r="M28" s="15"/>
     </row>
-    <row r="29" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="3" t="s">
         <v>115</v>
       </c>
@@ -3277,33 +3331,33 @@
       <c r="D29" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="E29" s="37" t="b">
+      <c r="E29" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F29" s="3">
         <v>3</v>
       </c>
-      <c r="G29" s="31" t="s">
+      <c r="G29" s="24" t="s">
         <v>372</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="23" t="s">
         <v>116</v>
       </c>
       <c r="B30" s="23" t="s">
         <v>323</v>
       </c>
-      <c r="C30" s="32" t="s">
+      <c r="C30" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="D30" s="32" t="s">
+      <c r="D30" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E30" s="32" t="b">
+      <c r="E30" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F30" s="15">
@@ -3321,7 +3375,7 @@
       <c r="L30" s="15"/>
       <c r="M30" s="15"/>
     </row>
-    <row r="31" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="3" t="s">
         <v>119</v>
       </c>
@@ -3334,33 +3388,33 @@
       <c r="D31" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="E31" s="37" t="b">
+      <c r="E31" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F31" s="3">
         <v>5</v>
       </c>
-      <c r="G31" s="31" t="s">
+      <c r="G31" s="24" t="s">
         <v>372</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="23" t="s">
         <v>121</v>
       </c>
       <c r="B32" s="23" t="s">
         <v>321</v>
       </c>
-      <c r="C32" s="32" t="s">
+      <c r="C32" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="D32" s="32" t="s">
+      <c r="D32" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E32" s="32" t="b">
+      <c r="E32" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F32" s="15">
@@ -3378,7 +3432,7 @@
       <c r="L32" s="15"/>
       <c r="M32" s="15"/>
     </row>
-    <row r="33" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="3" t="s">
         <v>123</v>
       </c>
@@ -3391,33 +3445,33 @@
       <c r="D33" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="E33" s="37" t="b">
+      <c r="E33" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F33" s="3">
         <v>6</v>
       </c>
-      <c r="G33" s="31" t="s">
+      <c r="G33" s="24" t="s">
         <v>371</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="23" t="s">
         <v>125</v>
       </c>
       <c r="B34" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="C34" s="32" t="s">
+      <c r="C34" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="D34" s="32" t="s">
+      <c r="D34" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E34" s="32" t="b">
+      <c r="E34" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F34" s="15">
@@ -3435,7 +3489,7 @@
       <c r="L34" s="15"/>
       <c r="M34" s="15"/>
     </row>
-    <row r="35" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="3" t="s">
         <v>127</v>
       </c>
@@ -3448,33 +3502,33 @@
       <c r="D35" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="E35" s="37" t="b">
+      <c r="E35" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F35" s="3">
         <v>12</v>
       </c>
-      <c r="G35" s="31" t="s">
+      <c r="G35" s="24" t="s">
         <v>6</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="23" t="s">
         <v>184</v>
       </c>
       <c r="B36" s="23" t="s">
         <v>326</v>
       </c>
-      <c r="C36" s="32" t="s">
+      <c r="C36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D36" s="32" t="s">
+      <c r="D36" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E36" s="32" t="b">
+      <c r="E36" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F36" s="15">
@@ -3483,7 +3537,7 @@
       <c r="G36" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="H36" s="35" t="s">
+      <c r="H36" s="15" t="s">
         <v>485</v>
       </c>
       <c r="I36" s="15"/>
@@ -3492,7 +3546,7 @@
       <c r="L36" s="15"/>
       <c r="M36" s="15"/>
     </row>
-    <row r="37" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="3" t="s">
         <v>185</v>
       </c>
@@ -3505,33 +3559,33 @@
       <c r="D37" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="E37" s="37" t="b">
+      <c r="E37" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F37" s="3">
         <v>5</v>
       </c>
-      <c r="G37" s="31" t="s">
+      <c r="G37" s="24" t="s">
         <v>375</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="23" t="s">
         <v>131</v>
       </c>
       <c r="B38" s="23" t="s">
         <v>327</v>
       </c>
-      <c r="C38" s="32" t="s">
+      <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="E38" s="32" t="b">
+      <c r="E38" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F38" s="15">
@@ -3540,7 +3594,7 @@
       <c r="G38" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="H38" s="35" t="s">
+      <c r="H38" s="15" t="s">
         <v>485</v>
       </c>
       <c r="I38" s="15"/>
@@ -3549,7 +3603,7 @@
       <c r="L38" s="15"/>
       <c r="M38" s="15"/>
     </row>
-    <row r="39" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="3" t="s">
         <v>240</v>
       </c>
@@ -3562,33 +3616,33 @@
       <c r="D39" s="24" t="s">
         <v>239</v>
       </c>
-      <c r="E39" s="37" t="b">
+      <c r="E39" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F39" s="3">
         <v>7</v>
       </c>
-      <c r="G39" s="31" t="s">
+      <c r="G39" s="24" t="s">
         <v>373</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="23" t="s">
         <v>153</v>
       </c>
       <c r="B40" s="23" t="s">
         <v>330</v>
       </c>
-      <c r="C40" s="32" t="s">
+      <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D40" s="32" t="s">
+      <c r="D40" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E40" s="32" t="b">
+      <c r="E40" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F40" s="15">
@@ -3606,7 +3660,7 @@
       <c r="L40" s="15"/>
       <c r="M40" s="15"/>
     </row>
-    <row r="41" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="3" t="s">
         <v>165</v>
       </c>
@@ -3619,33 +3673,33 @@
       <c r="D41" s="24" t="s">
         <v>134</v>
       </c>
-      <c r="E41" s="37" t="b">
+      <c r="E41" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F41" s="3">
         <v>4</v>
       </c>
-      <c r="G41" s="31" t="s">
+      <c r="G41" s="24" t="s">
         <v>369</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="23" t="s">
         <v>164</v>
       </c>
       <c r="B42" s="23" t="s">
         <v>332</v>
       </c>
-      <c r="C42" s="32" t="s">
+      <c r="C42" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="D42" s="32" t="s">
+      <c r="D42" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E42" s="32" t="b">
+      <c r="E42" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F42" s="15">
@@ -3663,7 +3717,7 @@
       <c r="L42" s="15"/>
       <c r="M42" s="15"/>
     </row>
-    <row r="43" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="3" t="s">
         <v>173</v>
       </c>
@@ -3676,33 +3730,33 @@
       <c r="D43" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="E43" s="37" t="b">
+      <c r="E43" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F43" s="3">
         <v>6</v>
       </c>
-      <c r="G43" s="31" t="s">
+      <c r="G43" s="24" t="s">
         <v>372</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="23" t="s">
         <v>172</v>
       </c>
       <c r="B44" s="23" t="s">
         <v>334</v>
       </c>
-      <c r="C44" s="32" t="s">
+      <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D44" s="32" t="s">
+      <c r="D44" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E44" s="32" t="b">
+      <c r="E44" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F44" s="15">
@@ -3711,7 +3765,7 @@
       <c r="G44" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="H44" s="35" t="s">
+      <c r="H44" s="15" t="s">
         <v>485</v>
       </c>
       <c r="I44" s="15"/>
@@ -3720,7 +3774,7 @@
       <c r="L44" s="15"/>
       <c r="M44" s="15"/>
     </row>
-    <row r="45" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="3" t="s">
         <v>155</v>
       </c>
@@ -3733,33 +3787,33 @@
       <c r="D45" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="E45" s="37" t="b">
+      <c r="E45" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F45" s="3">
         <v>12</v>
       </c>
-      <c r="G45" s="31" t="s">
+      <c r="G45" s="24" t="s">
         <v>378</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="25" t="s">
         <v>159</v>
       </c>
       <c r="B46" s="25" t="s">
         <v>336</v>
       </c>
-      <c r="C46" s="32" t="s">
+      <c r="C46" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="D46" s="32" t="s">
+      <c r="D46" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="E46" s="32" t="b">
+      <c r="E46" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F46" s="15">
@@ -3777,7 +3831,7 @@
       <c r="L46" s="15"/>
       <c r="M46" s="15"/>
     </row>
-    <row r="47" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="3" t="s">
         <v>160</v>
       </c>
@@ -3790,33 +3844,33 @@
       <c r="D47" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="E47" s="37" t="b">
+      <c r="E47" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F47" s="3">
         <v>3</v>
       </c>
-      <c r="G47" s="31" t="s">
+      <c r="G47" s="24" t="s">
         <v>371</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="25" t="s">
         <v>175</v>
       </c>
       <c r="B48" s="25" t="s">
         <v>338</v>
       </c>
-      <c r="C48" s="32" t="s">
+      <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D48" s="32" t="s">
+      <c r="D48" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E48" s="32" t="b">
+      <c r="E48" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F48" s="15">
@@ -3834,7 +3888,7 @@
       <c r="L48" s="15"/>
       <c r="M48" s="15"/>
     </row>
-    <row r="49" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="3" t="s">
         <v>174</v>
       </c>
@@ -3847,33 +3901,33 @@
       <c r="D49" s="24" t="s">
         <v>339</v>
       </c>
-      <c r="E49" s="37" t="b">
+      <c r="E49" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F49" s="3">
         <v>5</v>
       </c>
-      <c r="G49" s="31" t="s">
+      <c r="G49" s="24" t="s">
         <v>378</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="23" t="s">
         <v>154</v>
       </c>
       <c r="B50" s="23" t="s">
         <v>341</v>
       </c>
-      <c r="C50" s="32" t="s">
+      <c r="C50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D50" s="32" t="s">
+      <c r="D50" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E50" s="32" t="b">
+      <c r="E50" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F50" s="15">
@@ -3891,7 +3945,7 @@
       <c r="L50" s="15"/>
       <c r="M50" s="15"/>
     </row>
-    <row r="51" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="3" t="s">
         <v>161</v>
       </c>
@@ -3904,33 +3958,33 @@
       <c r="D51" s="24" t="s">
         <v>342</v>
       </c>
-      <c r="E51" s="37" t="b">
+      <c r="E51" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F51" s="3">
         <v>14</v>
       </c>
-      <c r="G51" s="31" t="s">
+      <c r="G51" s="24" t="s">
         <v>381</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="23" t="s">
         <v>156</v>
       </c>
       <c r="B52" s="23" t="s">
         <v>344</v>
       </c>
-      <c r="C52" s="32" t="s">
+      <c r="C52" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="D52" s="32" t="s">
+      <c r="D52" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="E52" s="32" t="b">
+      <c r="E52" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F52" s="15">
@@ -3948,7 +4002,7 @@
       <c r="L52" s="15"/>
       <c r="M52" s="15"/>
     </row>
-    <row r="53" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="3" t="s">
         <v>176</v>
       </c>
@@ -3961,33 +4015,33 @@
       <c r="D53" s="24" t="s">
         <v>141</v>
       </c>
-      <c r="E53" s="37" t="b">
+      <c r="E53" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F53" s="3">
         <v>10</v>
       </c>
-      <c r="G53" s="31" t="s">
+      <c r="G53" s="24" t="s">
         <v>375</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="23" t="s">
         <v>163</v>
       </c>
       <c r="B54" s="23" t="s">
         <v>345</v>
       </c>
-      <c r="C54" s="32" t="s">
+      <c r="C54" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D54" s="32" t="s">
+      <c r="D54" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E54" s="32" t="b">
+      <c r="E54" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F54" s="15">
@@ -4005,7 +4059,7 @@
       <c r="L54" s="15"/>
       <c r="M54" s="15"/>
     </row>
-    <row r="55" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="3" t="s">
         <v>162</v>
       </c>
@@ -4018,33 +4072,33 @@
       <c r="D55" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="E55" s="37" t="b">
+      <c r="E55" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F55" s="3">
         <v>6</v>
       </c>
-      <c r="G55" s="31" t="s">
+      <c r="G55" s="24" t="s">
         <v>377</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="23" t="s">
         <v>177</v>
       </c>
       <c r="B56" s="23" t="s">
         <v>349</v>
       </c>
-      <c r="C56" s="32" t="s">
+      <c r="C56" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="D56" s="32" t="s">
+      <c r="D56" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E56" s="32" t="b">
+      <c r="E56" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F56" s="15">
@@ -4053,7 +4107,7 @@
       <c r="G56" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H56" s="35" t="s">
+      <c r="H56" s="15" t="s">
         <v>486</v>
       </c>
       <c r="I56" s="15"/>
@@ -4062,7 +4116,7 @@
       <c r="L56" s="15"/>
       <c r="M56" s="15"/>
     </row>
-    <row r="57" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="3" t="s">
         <v>178</v>
       </c>
@@ -4075,33 +4129,33 @@
       <c r="D57" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="E57" s="37" t="b">
+      <c r="E57" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F57" s="3">
         <v>4</v>
       </c>
-      <c r="G57" s="31" t="s">
+      <c r="G57" s="24" t="s">
         <v>383</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="23" t="s">
         <v>179</v>
       </c>
       <c r="B58" s="23" t="s">
         <v>350</v>
       </c>
-      <c r="C58" s="32" t="s">
+      <c r="C58" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="D58" s="32" t="s">
+      <c r="D58" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E58" s="32" t="b">
+      <c r="E58" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F58" s="15">
@@ -4110,7 +4164,7 @@
       <c r="G58" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="H58" s="35" t="s">
+      <c r="H58" s="15" t="s">
         <v>487</v>
       </c>
       <c r="I58" s="15"/>
@@ -4119,7 +4173,7 @@
       <c r="L58" s="15"/>
       <c r="M58" s="15"/>
     </row>
-    <row r="59" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="3" t="s">
         <v>180</v>
       </c>
@@ -4132,33 +4186,33 @@
       <c r="D59" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="E59" s="37" t="b">
+      <c r="E59" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F59" s="3">
         <v>4</v>
       </c>
-      <c r="G59" s="31" t="s">
+      <c r="G59" s="24" t="s">
         <v>376</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="23" t="s">
         <v>181</v>
       </c>
       <c r="B60" s="23" t="s">
         <v>353</v>
       </c>
-      <c r="C60" s="32" t="s">
+      <c r="C60" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="D60" s="32" t="s">
+      <c r="D60" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E60" s="32" t="b">
+      <c r="E60" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F60" s="15">
@@ -4176,7 +4230,7 @@
       <c r="L60" s="15"/>
       <c r="M60" s="15"/>
     </row>
-    <row r="61" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="3" t="s">
         <v>182</v>
       </c>
@@ -4189,33 +4243,33 @@
       <c r="D61" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="E61" s="37" t="b">
+      <c r="E61" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F61" s="3">
         <v>4</v>
       </c>
-      <c r="G61" s="31" t="s">
+      <c r="G61" s="24" t="s">
         <v>384</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="25" t="s">
         <v>183</v>
       </c>
       <c r="B62" s="25" t="s">
         <v>354</v>
       </c>
-      <c r="C62" s="32" t="s">
+      <c r="C62" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="D62" s="32" t="s">
+      <c r="D62" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E62" s="32" t="b">
+      <c r="E62" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F62" s="15">
@@ -4224,7 +4278,7 @@
       <c r="G62" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="H62" s="35" t="s">
+      <c r="H62" s="15" t="s">
         <v>487</v>
       </c>
       <c r="I62" s="15"/>
@@ -4233,7 +4287,7 @@
       <c r="L62" s="15"/>
       <c r="M62" s="15"/>
     </row>
-    <row r="63" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="3" t="s">
         <v>186</v>
       </c>
@@ -4246,33 +4300,33 @@
       <c r="D63" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="E63" s="37" t="b">
+      <c r="E63" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F63" s="3">
         <v>6</v>
       </c>
-      <c r="G63" s="31" t="s">
+      <c r="G63" s="24" t="s">
         <v>371</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="25" t="s">
         <v>187</v>
       </c>
       <c r="B64" s="25" t="s">
         <v>357</v>
       </c>
-      <c r="C64" s="32" t="s">
+      <c r="C64" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D64" s="32" t="s">
+      <c r="D64" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E64" s="32" t="b">
+      <c r="E64" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F64" s="15">
@@ -4281,7 +4335,7 @@
       <c r="G64" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="H64" s="35" t="s">
+      <c r="H64" s="15" t="s">
         <v>487</v>
       </c>
       <c r="I64" s="15"/>
@@ -4290,7 +4344,7 @@
       <c r="L64" s="15"/>
       <c r="M64" s="15"/>
     </row>
-    <row r="65" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="3" t="s">
         <v>188</v>
       </c>
@@ -4303,33 +4357,33 @@
       <c r="D65" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="E65" s="37" t="b">
+      <c r="E65" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F65" s="3">
         <v>3</v>
       </c>
-      <c r="G65" s="31" t="s">
+      <c r="G65" s="24" t="s">
         <v>370</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="23" t="s">
         <v>494</v>
       </c>
       <c r="B66" s="23" t="s">
         <v>494</v>
       </c>
-      <c r="C66" s="32" t="s">
+      <c r="C66" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="D66" s="32" t="s">
+      <c r="D66" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E66" s="32" t="b">
+      <c r="E66" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F66" s="15">
@@ -4338,7 +4392,7 @@
       <c r="G66" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="H66" s="35" t="s">
+      <c r="H66" s="15" t="s">
         <v>493</v>
       </c>
       <c r="I66" s="15"/>
@@ -4347,7 +4401,7 @@
       <c r="L66" s="15"/>
       <c r="M66" s="15"/>
     </row>
-    <row r="67" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="3" t="s">
         <v>189</v>
       </c>
@@ -4360,33 +4414,33 @@
       <c r="D67" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="E67" s="37" t="b">
+      <c r="E67" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F67" s="3">
         <v>5</v>
       </c>
-      <c r="G67" s="31" t="s">
+      <c r="G67" s="24" t="s">
         <v>372</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="25" t="s">
         <v>190</v>
       </c>
       <c r="B68" s="25" t="s">
         <v>359</v>
       </c>
-      <c r="C68" s="32" t="s">
+      <c r="C68" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="D68" s="32" t="s">
+      <c r="D68" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E68" s="32" t="b">
+      <c r="E68" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F68" s="15">
@@ -4404,7 +4458,7 @@
       <c r="L68" s="15"/>
       <c r="M68" s="15"/>
     </row>
-    <row r="69" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="3" t="s">
         <v>192</v>
       </c>
@@ -4417,33 +4471,33 @@
       <c r="D69" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="E69" s="37" t="b">
+      <c r="E69" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F69" s="3">
         <v>4</v>
       </c>
-      <c r="G69" s="31" t="s">
+      <c r="G69" s="24" t="s">
         <v>375</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="25" t="s">
         <v>193</v>
       </c>
       <c r="B70" s="25" t="s">
         <v>361</v>
       </c>
-      <c r="C70" s="32" t="s">
+      <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D70" s="32" t="s">
+      <c r="D70" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E70" s="32" t="b">
+      <c r="E70" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F70" s="15">
@@ -4452,7 +4506,7 @@
       <c r="G70" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="H70" s="35" t="s">
+      <c r="H70" s="15" t="s">
         <v>491</v>
       </c>
       <c r="I70" s="15"/>
@@ -4461,7 +4515,7 @@
       <c r="L70" s="15"/>
       <c r="M70" s="15"/>
     </row>
-    <row r="71" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="3" t="s">
         <v>191</v>
       </c>
@@ -4474,33 +4528,33 @@
       <c r="D71" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="E71" s="37" t="b">
+      <c r="E71" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F71" s="3">
         <v>8</v>
       </c>
-      <c r="G71" s="31" t="s">
+      <c r="G71" s="24" t="s">
         <v>389</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="25" t="s">
         <v>194</v>
       </c>
       <c r="B72" s="25" t="s">
         <v>363</v>
       </c>
-      <c r="C72" s="32" t="s">
+      <c r="C72" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="D72" s="32" t="s">
+      <c r="D72" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E72" s="32" t="b">
+      <c r="E72" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F72" s="15">
@@ -4509,7 +4563,7 @@
       <c r="G72" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="H72" s="35" t="s">
+      <c r="H72" s="15" t="s">
         <v>487</v>
       </c>
       <c r="I72" s="15"/>
@@ -4518,7 +4572,7 @@
       <c r="L72" s="15"/>
       <c r="M72" s="15"/>
     </row>
-    <row r="73" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="3" t="s">
         <v>195</v>
       </c>
@@ -4531,33 +4585,33 @@
       <c r="D73" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="E73" s="37" t="b">
+      <c r="E73" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F73" s="3">
         <v>3</v>
       </c>
-      <c r="G73" s="31" t="s">
+      <c r="G73" s="24" t="s">
         <v>376</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="25" t="s">
         <v>196</v>
       </c>
       <c r="B74" s="25" t="s">
         <v>365</v>
       </c>
-      <c r="C74" s="32" t="s">
+      <c r="C74" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="D74" s="32" t="s">
+      <c r="D74" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="E74" s="32" t="b">
+      <c r="E74" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F74" s="15">
@@ -4566,7 +4620,7 @@
       <c r="G74" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="H74" s="35" t="s">
+      <c r="H74" s="15" t="s">
         <v>491</v>
       </c>
       <c r="I74" s="15"/>
@@ -4575,7 +4629,7 @@
       <c r="L74" s="15"/>
       <c r="M74" s="15"/>
     </row>
-    <row r="75" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="3" t="s">
         <v>197</v>
       </c>
@@ -4588,34 +4642,34 @@
       <c r="D75" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="E75" s="37" t="b">
+      <c r="E75" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F75" s="3">
         <f>ROUND(F56*1.3,0)</f>
         <v>5</v>
       </c>
-      <c r="G75" s="31" t="s">
+      <c r="G75" s="24" t="s">
         <v>497</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="25" t="s">
         <v>198</v>
       </c>
       <c r="B76" s="25" t="s">
         <v>198</v>
       </c>
-      <c r="C76" s="32" t="s">
+      <c r="C76" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="D76" s="32" t="s">
+      <c r="D76" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E76" s="32" t="b">
+      <c r="E76" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F76" s="15">
@@ -4634,7 +4688,7 @@
       <c r="L76" s="15"/>
       <c r="M76" s="15"/>
     </row>
-    <row r="77" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="3" t="s">
         <v>199</v>
       </c>
@@ -4647,34 +4701,34 @@
       <c r="D77" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="E77" s="37" t="b">
+      <c r="E77" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F77" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G77" s="31" t="s">
+      <c r="G77" s="24" t="s">
         <v>499</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="25" t="s">
         <v>200</v>
       </c>
       <c r="B78" s="25" t="s">
         <v>200</v>
       </c>
-      <c r="C78" s="32" t="s">
+      <c r="C78" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="D78" s="32" t="s">
+      <c r="D78" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E78" s="32" t="b">
+      <c r="E78" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F78" s="15">
@@ -4693,7 +4747,7 @@
       <c r="L78" s="15"/>
       <c r="M78" s="15"/>
     </row>
-    <row r="79" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="3" t="s">
         <v>201</v>
       </c>
@@ -4706,34 +4760,34 @@
       <c r="D79" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="E79" s="37" t="b">
+      <c r="E79" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F79" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="G79" s="31" t="s">
+      <c r="G79" s="24" t="s">
         <v>501</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="80" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="25" t="s">
         <v>202</v>
       </c>
       <c r="B80" s="25" t="s">
         <v>202</v>
       </c>
-      <c r="C80" s="32" t="s">
+      <c r="C80" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="D80" s="32" t="s">
+      <c r="D80" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E80" s="32" t="b">
+      <c r="E80" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F80" s="15">
@@ -4752,7 +4806,7 @@
       <c r="L80" s="15"/>
       <c r="M80" s="15"/>
     </row>
-    <row r="81" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="3" t="s">
         <v>203</v>
       </c>
@@ -4765,34 +4819,34 @@
       <c r="D81" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="E81" s="37" t="b">
+      <c r="E81" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F81" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="G81" s="31" t="s">
+      <c r="G81" s="24" t="s">
         <v>502</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="82" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="25" t="s">
         <v>204</v>
       </c>
       <c r="B82" s="25" t="s">
         <v>204</v>
       </c>
-      <c r="C82" s="32" t="s">
+      <c r="C82" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="D82" s="32" t="s">
+      <c r="D82" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="E82" s="32" t="b">
+      <c r="E82" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F82" s="15">
@@ -4811,7 +4865,7 @@
       <c r="L82" s="15"/>
       <c r="M82" s="15"/>
     </row>
-    <row r="83" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="3" t="s">
         <v>205</v>
       </c>
@@ -4824,34 +4878,34 @@
       <c r="D83" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="E83" s="37" t="b">
+      <c r="E83" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F83" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G83" s="31" t="s">
+      <c r="G83" s="24" t="s">
         <v>504</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="84" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="25" t="s">
         <v>206</v>
       </c>
       <c r="B84" s="25" t="s">
         <v>206</v>
       </c>
-      <c r="C84" s="32" t="s">
+      <c r="C84" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="D84" s="32" t="s">
+      <c r="D84" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E84" s="32" t="b">
+      <c r="E84" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F84" s="15">
@@ -4870,7 +4924,7 @@
       <c r="L84" s="15"/>
       <c r="M84" s="15"/>
     </row>
-    <row r="85" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="3" t="s">
         <v>495</v>
       </c>
@@ -4883,34 +4937,34 @@
       <c r="D85" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="E85" s="37" t="b">
+      <c r="E85" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F85" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="G85" s="31" t="s">
+      <c r="G85" s="24" t="s">
         <v>506</v>
       </c>
       <c r="H85" s="3" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="25" t="s">
         <v>207</v>
       </c>
       <c r="B86" s="25" t="s">
         <v>207</v>
       </c>
-      <c r="C86" s="32" t="s">
+      <c r="C86" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="D86" s="32" t="s">
+      <c r="D86" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E86" s="32" t="b">
+      <c r="E86" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F86" s="15">
@@ -4929,7 +4983,7 @@
       <c r="L86" s="15"/>
       <c r="M86" s="15"/>
     </row>
-    <row r="87" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="3" t="s">
         <v>208</v>
       </c>
@@ -4942,34 +4996,34 @@
       <c r="D87" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E87" s="37" t="b">
+      <c r="E87" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F87" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="G87" s="31" t="s">
+      <c r="G87" s="24" t="s">
         <v>503</v>
       </c>
       <c r="H87" s="3" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="25" t="s">
         <v>209</v>
       </c>
       <c r="B88" s="25" t="s">
         <v>209</v>
       </c>
-      <c r="C88" s="32" t="s">
+      <c r="C88" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="D88" s="32" t="s">
+      <c r="D88" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="E88" s="32" t="b">
+      <c r="E88" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F88" s="15">
@@ -4988,7 +5042,7 @@
       <c r="L88" s="15"/>
       <c r="M88" s="15"/>
     </row>
-    <row r="89" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="3" t="s">
         <v>210</v>
       </c>
@@ -5001,34 +5055,34 @@
       <c r="D89" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="E89" s="37" t="b">
+      <c r="E89" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F89" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="G89" s="31" t="s">
+      <c r="G89" s="24" t="s">
         <v>509</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="90" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="25" t="s">
         <v>211</v>
       </c>
       <c r="B90" s="25" t="s">
         <v>211</v>
       </c>
-      <c r="C90" s="32" t="s">
+      <c r="C90" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="D90" s="32" t="s">
+      <c r="D90" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="E90" s="32" t="b">
+      <c r="E90" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F90" s="15">
@@ -5047,7 +5101,7 @@
       <c r="L90" s="15"/>
       <c r="M90" s="15"/>
     </row>
-    <row r="91" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="3" t="s">
         <v>212</v>
       </c>
@@ -5060,34 +5114,34 @@
       <c r="D91" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="E91" s="37" t="b">
+      <c r="E91" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F91" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="G91" s="31" t="s">
+      <c r="G91" s="24" t="s">
         <v>511</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="92" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="25" t="s">
         <v>213</v>
       </c>
       <c r="B92" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="C92" s="32" t="s">
+      <c r="C92" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="D92" s="32" t="s">
+      <c r="D92" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E92" s="32" t="b">
+      <c r="E92" s="1" t="b">
         <v>0</v>
       </c>
       <c r="F92" s="15">
@@ -5106,7 +5160,7 @@
       <c r="L92" s="15"/>
       <c r="M92" s="15"/>
     </row>
-    <row r="93" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="3" t="s">
         <v>214</v>
       </c>
@@ -5119,43 +5173,43 @@
       <c r="D93" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="E93" s="37" t="b">
+      <c r="E93" s="2" t="b">
         <v>0</v>
       </c>
       <c r="F93" s="3">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="G93" s="31" t="s">
+      <c r="G93" s="24" t="s">
         <v>513</v>
       </c>
       <c r="H93" s="3" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="32" t="s">
+    <row r="94" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A94" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B94" s="32" t="s">
+      <c r="B94" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="C94" s="32" t="s">
+      <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D94" s="32" t="s">
+      <c r="D94" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="E94" s="32" t="b">
+      <c r="E94" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="F94" s="32">
+      <c r="F94" s="1">
         <v>2</v>
       </c>
-      <c r="G94" s="32" t="s">
+      <c r="G94" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="H94" s="32" t="s">
+      <c r="H94" s="1" t="s">
         <v>459</v>
       </c>
       <c r="I94" s="15"/>
@@ -5164,7 +5218,7 @@
       <c r="L94" s="15"/>
       <c r="M94" s="15"/>
     </row>
-    <row r="95" spans="1:13" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="24" t="s">
         <v>400</v>
       </c>
@@ -5177,7 +5231,7 @@
       <c r="D95" s="24" t="s">
         <v>391</v>
       </c>
-      <c r="E95" s="37" t="b">
+      <c r="E95" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F95" s="24">
@@ -5190,33 +5244,33 @@
         <v>413</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A96" s="32" t="s">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A96" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B96" s="32" t="s">
+      <c r="B96" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="C96" s="32" t="s">
+      <c r="C96" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="D96" s="32" t="s">
+      <c r="D96" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="E96" s="32" t="b">
+      <c r="E96" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="F96" s="32">
+      <c r="F96" s="1">
         <v>5</v>
       </c>
-      <c r="G96" s="32" t="s">
+      <c r="G96" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="H96" s="32" t="s">
+      <c r="H96" s="1" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A97" s="24" t="s">
         <v>402</v>
       </c>
@@ -5229,10 +5283,10 @@
       <c r="D97" s="24" t="s">
         <v>394</v>
       </c>
-      <c r="E97" s="37" t="b">
+      <c r="E97" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="F97" s="38"/>
+      <c r="F97" s="29"/>
       <c r="G97" s="24" t="s">
         <v>6</v>
       </c>
@@ -5240,33 +5294,33 @@
         <v>413</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="32" t="s">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A98" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B98" s="32" t="s">
+      <c r="B98" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="C98" s="32" t="s">
+      <c r="C98" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="D98" s="32" t="s">
+      <c r="D98" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="E98" s="32" t="b">
+      <c r="E98" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="F98" s="32">
+      <c r="F98" s="1">
         <v>6</v>
       </c>
-      <c r="G98" s="32" t="s">
+      <c r="G98" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="H98" s="32" t="s">
+      <c r="H98" s="1" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A99" s="24" t="s">
         <v>397</v>
       </c>
@@ -5279,7 +5333,7 @@
       <c r="D99" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="E99" s="37" t="b">
+      <c r="E99" s="2" t="b">
         <v>1</v>
       </c>
       <c r="F99" s="24">
@@ -5292,29 +5346,29 @@
         <v>485</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="32" t="s">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A100" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B100" s="32" t="s">
+      <c r="B100" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="C100" s="32" t="s">
+      <c r="C100" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="D100" s="32" t="s">
+      <c r="D100" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="E100" s="32" t="b">
+      <c r="E100" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="F100" s="32">
+      <c r="F100" s="1">
         <v>6</v>
       </c>
-      <c r="G100" s="32" t="s">
+      <c r="G100" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H100" s="32" t="s">
+      <c r="H100" s="1" t="s">
         <v>492</v>
       </c>
     </row>
@@ -5327,23 +5381,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{084DBB7A-B5EB-40AD-BCD5-5AECD2B1DA93}">
-  <dimension ref="A1:K44"/>
-  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L44"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="5.58203125" style="41" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.25" style="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.25" style="24" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="103.9140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="5.5546875" style="32" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.21875" style="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.21875" style="24" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="103.88671875" style="24" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="41.33203125" style="24" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="255.75" style="24" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.58203125" style="24" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="255.77734375" style="24" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" style="24" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="26" style="24" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.1640625" style="24" customWidth="1"/>
-    <col min="11" max="11" width="25.83203125" style="24" customWidth="1"/>
-    <col min="12" max="16384" width="8.9140625" style="24"/>
+    <col min="10" max="10" width="17.109375" style="24" customWidth="1"/>
+    <col min="11" max="11" width="25.77734375" style="24" customWidth="1"/>
+    <col min="12" max="12" width="20.21875" style="24" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="40" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="31" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -5377,8 +5432,11 @@
       <c r="K1" s="22" t="s">
         <v>542</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L1" s="35" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>7</v>
       </c>
@@ -5388,31 +5446,34 @@
       <c r="C2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="32" t="s">
+      <c r="E2" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="G2" s="32" t="s">
+      <c r="G2" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="H2" s="32">
+      <c r="H2" s="1">
         <v>5</v>
       </c>
-      <c r="I2" s="32" t="s">
+      <c r="I2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="32" t="str">
+      <c r="J2" s="1" t="str">
         <f>A3</f>
         <v>1-2</v>
       </c>
-      <c r="K2" s="42"/>
-    </row>
-    <row r="3" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K2" s="33"/>
+      <c r="L2" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>146</v>
       </c>
@@ -5422,34 +5483,37 @@
       <c r="C3" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="E3" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="F3" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="G3" s="33" t="s">
+      <c r="G3" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="H3" s="33">
+      <c r="H3" s="2">
         <v>5</v>
       </c>
-      <c r="I3" s="37" t="s">
+      <c r="I3" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="J3" s="33" t="str">
+      <c r="J3" s="2" t="str">
         <f t="shared" ref="J3:J42" si="0">A4</f>
         <v>1-3</v>
       </c>
-      <c r="K3" s="33" t="str">
+      <c r="K3" s="2" t="str">
         <f>B2</f>
         <v>1-1</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L3" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
         <v>147</v>
       </c>
@@ -5459,38 +5523,41 @@
       <c r="C4" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="E4" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="F4" s="32" t="s">
+      <c r="F4" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="G4" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="H4" s="32">
+      <c r="H4" s="1">
         <v>5</v>
       </c>
-      <c r="I4" s="32" t="s">
+      <c r="I4" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="J4" s="32" t="str">
+      <c r="J4" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1-4</v>
       </c>
-      <c r="K4" s="32" t="str">
+      <c r="K4" s="1" t="str">
         <f t="shared" ref="K4:K42" si="1">B3</f>
         <v>1-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="41" t="s">
+      <c r="L4" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="32" t="s">
         <v>242</v>
       </c>
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="32" t="s">
         <v>242</v>
       </c>
       <c r="C5" s="24" t="s">
@@ -5499,31 +5566,34 @@
       <c r="D5" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="E5" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="F5" s="33" t="s">
+      <c r="F5" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="G5" s="33" t="s">
+      <c r="G5" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="H5" s="33">
+      <c r="H5" s="2">
         <v>5</v>
       </c>
-      <c r="I5" s="37" t="s">
+      <c r="I5" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="J5" s="33" t="str">
+      <c r="J5" s="2" t="str">
         <f t="shared" si="0"/>
         <v>1-5</v>
       </c>
-      <c r="K5" s="33" t="str">
+      <c r="K5" s="2" t="str">
         <f t="shared" si="1"/>
         <v>1-3</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L5" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
         <v>243</v>
       </c>
@@ -5533,36 +5603,39 @@
       <c r="C6" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="34" t="s">
+      <c r="E6" s="28" t="s">
         <v>545</v>
       </c>
-      <c r="F6" s="34" t="s">
+      <c r="F6" s="28" t="s">
         <v>515</v>
       </c>
-      <c r="G6" s="34" t="s">
+      <c r="G6" s="28" t="s">
         <v>515</v>
       </c>
-      <c r="H6" s="34"/>
-      <c r="I6" s="34" t="s">
+      <c r="H6" s="28"/>
+      <c r="I6" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="J6" s="34" t="str">
+      <c r="J6" s="28" t="str">
         <f t="shared" si="0"/>
         <v>1-6</v>
       </c>
-      <c r="K6" s="34" t="str">
+      <c r="K6" s="28" t="str">
         <f t="shared" si="1"/>
         <v>1-4</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="41" t="s">
+      <c r="L6" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="32" t="s">
         <v>244</v>
       </c>
-      <c r="B7" s="41" t="s">
+      <c r="B7" s="32" t="s">
         <v>244</v>
       </c>
       <c r="C7" s="24" t="s">
@@ -5571,10 +5644,10 @@
       <c r="D7" s="24" t="s">
         <v>286</v>
       </c>
-      <c r="E7" s="33" t="s">
+      <c r="E7" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="F7" s="36" t="s">
+      <c r="F7" s="24" t="s">
         <v>515</v>
       </c>
       <c r="G7" s="24" t="s">
@@ -5583,19 +5656,22 @@
       <c r="H7" s="24">
         <v>5</v>
       </c>
-      <c r="I7" s="37" t="s">
+      <c r="I7" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="J7" s="33" t="str">
+      <c r="J7" s="2" t="str">
         <f t="shared" si="0"/>
         <v>1-7</v>
       </c>
-      <c r="K7" s="33" t="str">
+      <c r="K7" s="2" t="str">
         <f t="shared" si="1"/>
         <v>1-5</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L7" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
         <v>245</v>
       </c>
@@ -5605,38 +5681,41 @@
       <c r="C8" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="E8" s="32" t="s">
+      <c r="E8" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="F8" s="32" t="s">
+      <c r="F8" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="G8" s="32" t="s">
+      <c r="G8" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="1">
         <v>6</v>
       </c>
-      <c r="I8" s="32" t="s">
+      <c r="I8" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="J8" s="32" t="str">
+      <c r="J8" s="1" t="str">
         <f t="shared" si="0"/>
         <v>2-1</v>
       </c>
-      <c r="K8" s="32" t="str">
+      <c r="K8" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1-6</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="41" t="s">
+      <c r="L8" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="32" t="s">
         <v>246</v>
       </c>
-      <c r="B9" s="41" t="s">
+      <c r="B9" s="32" t="s">
         <v>246</v>
       </c>
       <c r="C9" s="24" t="s">
@@ -5645,10 +5724,10 @@
       <c r="D9" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="E9" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="F9" s="36" t="s">
+      <c r="F9" s="24" t="s">
         <v>515</v>
       </c>
       <c r="G9" s="24" t="s">
@@ -5657,19 +5736,22 @@
       <c r="H9" s="24">
         <v>6</v>
       </c>
-      <c r="I9" s="37" t="s">
+      <c r="I9" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="J9" s="33" t="str">
+      <c r="J9" s="2" t="str">
         <f t="shared" si="0"/>
         <v>2-2</v>
       </c>
-      <c r="K9" s="33" t="str">
+      <c r="K9" s="2" t="str">
         <f t="shared" si="1"/>
         <v>1-7</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L9" s="24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
         <v>247</v>
       </c>
@@ -5679,38 +5761,41 @@
       <c r="C10" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="F10" s="32" t="s">
+      <c r="F10" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="G10" s="32" t="s">
+      <c r="G10" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="H10" s="32">
+      <c r="H10" s="1">
         <v>6</v>
       </c>
-      <c r="I10" s="32" t="s">
+      <c r="I10" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="J10" s="32" t="str">
+      <c r="J10" s="1" t="str">
         <f t="shared" si="0"/>
         <v>2-3</v>
       </c>
-      <c r="K10" s="32" t="str">
+      <c r="K10" s="1" t="str">
         <f t="shared" si="1"/>
         <v>2-1</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="41" t="s">
+      <c r="L10" s="37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="32" t="s">
         <v>248</v>
       </c>
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="32" t="s">
         <v>248</v>
       </c>
       <c r="C11" s="24" t="s">
@@ -5719,10 +5804,10 @@
       <c r="D11" s="24" t="s">
         <v>289</v>
       </c>
-      <c r="E11" s="33" t="s">
+      <c r="E11" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="F11" s="36" t="s">
+      <c r="F11" s="24" t="s">
         <v>515</v>
       </c>
       <c r="G11" s="24" t="s">
@@ -5742,8 +5827,11 @@
         <f t="shared" si="1"/>
         <v>2-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L11" s="24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
         <v>249</v>
       </c>
@@ -5753,38 +5841,41 @@
       <c r="C12" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="32" t="s">
+      <c r="E12" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="F12" s="32" t="s">
+      <c r="F12" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="G12" s="32" t="s">
+      <c r="G12" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="H12" s="32">
+      <c r="H12" s="1">
         <v>6</v>
       </c>
-      <c r="I12" s="32" t="s">
+      <c r="I12" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="J12" s="32" t="str">
+      <c r="J12" s="1" t="str">
         <f t="shared" si="0"/>
         <v>2-5</v>
       </c>
-      <c r="K12" s="32" t="str">
+      <c r="K12" s="1" t="str">
         <f t="shared" si="1"/>
         <v>2-3</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="41" t="s">
+      <c r="L12" s="37">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="32" t="s">
         <v>250</v>
       </c>
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="32" t="s">
         <v>250</v>
       </c>
       <c r="C13" s="24" t="s">
@@ -5793,31 +5884,34 @@
       <c r="D13" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="33" t="s">
+      <c r="E13" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="F13" s="33" t="s">
+      <c r="F13" s="2" t="s">
         <v>515</v>
       </c>
       <c r="G13" s="24" t="s">
         <v>466</v>
       </c>
-      <c r="H13" s="33">
+      <c r="H13" s="2">
         <v>7</v>
       </c>
-      <c r="I13" s="33" t="s">
+      <c r="I13" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="J13" s="33" t="str">
+      <c r="J13" s="2" t="str">
         <f t="shared" si="0"/>
         <v>2-6</v>
       </c>
-      <c r="K13" s="33" t="str">
+      <c r="K13" s="2" t="str">
         <f t="shared" si="1"/>
         <v>2-4</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L13" s="24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
         <v>263</v>
       </c>
@@ -5827,38 +5921,41 @@
       <c r="C14" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E14" s="32" t="s">
+      <c r="E14" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="F14" s="32" t="s">
+      <c r="F14" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="G14" s="32" t="s">
+      <c r="G14" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="H14" s="32">
+      <c r="H14" s="1">
         <v>7</v>
       </c>
-      <c r="I14" s="32" t="s">
+      <c r="I14" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="J14" s="32" t="str">
+      <c r="J14" s="1" t="str">
         <f t="shared" si="0"/>
         <v>2-7</v>
       </c>
-      <c r="K14" s="32" t="str">
+      <c r="K14" s="1" t="str">
         <f t="shared" si="1"/>
         <v>2-5</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="41" t="s">
+      <c r="L14" s="38">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="32" t="s">
         <v>264</v>
       </c>
-      <c r="B15" s="41" t="s">
+      <c r="B15" s="32" t="s">
         <v>264</v>
       </c>
       <c r="C15" s="24" t="s">
@@ -5867,10 +5964,10 @@
       <c r="D15" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="33" t="s">
+      <c r="E15" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="F15" s="36" t="s">
+      <c r="F15" s="24" t="s">
         <v>515</v>
       </c>
       <c r="G15" s="24" t="s">
@@ -5890,8 +5987,11 @@
         <f t="shared" si="1"/>
         <v>2-6</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L15" s="24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="20" t="s">
         <v>265</v>
       </c>
@@ -5901,38 +6001,41 @@
       <c r="C16" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="F16" s="32" t="s">
+      <c r="F16" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="G16" s="32" t="s">
+      <c r="G16" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="H16" s="32">
+      <c r="H16" s="1">
         <v>7</v>
       </c>
-      <c r="I16" s="32" t="s">
+      <c r="I16" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="J16" s="32" t="str">
+      <c r="J16" s="1" t="str">
         <f t="shared" si="0"/>
         <v>2-9</v>
       </c>
-      <c r="K16" s="32" t="str">
+      <c r="K16" s="1" t="str">
         <f t="shared" si="1"/>
         <v>2-7</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="41" t="s">
+      <c r="L16" s="38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="32" t="s">
         <v>266</v>
       </c>
-      <c r="B17" s="41" t="s">
+      <c r="B17" s="32" t="s">
         <v>266</v>
       </c>
       <c r="C17" s="24" t="s">
@@ -5941,10 +6044,10 @@
       <c r="D17" s="24" t="s">
         <v>318</v>
       </c>
-      <c r="E17" s="33" t="s">
+      <c r="E17" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="F17" s="36" t="s">
+      <c r="F17" s="24" t="s">
         <v>449</v>
       </c>
       <c r="G17" s="24" t="s">
@@ -5964,8 +6067,11 @@
         <f t="shared" si="1"/>
         <v>2-8</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L17" s="24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="20" t="s">
         <v>251</v>
       </c>
@@ -5975,38 +6081,41 @@
       <c r="C18" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E18" s="32" t="s">
+      <c r="E18" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="F18" s="32" t="s">
+      <c r="F18" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="G18" s="32" t="s">
+      <c r="G18" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="H18" s="32">
+      <c r="H18" s="1">
         <v>8</v>
       </c>
-      <c r="I18" s="32" t="s">
+      <c r="I18" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="J18" s="32" t="str">
+      <c r="J18" s="1" t="str">
         <f t="shared" si="0"/>
         <v>3-2</v>
       </c>
-      <c r="K18" s="32" t="str">
+      <c r="K18" s="1" t="str">
         <f t="shared" si="1"/>
         <v>2-9</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="41" t="s">
+      <c r="L18" s="38">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="32" t="s">
         <v>252</v>
       </c>
-      <c r="B19" s="41" t="s">
+      <c r="B19" s="32" t="s">
         <v>252</v>
       </c>
       <c r="C19" s="24" t="s">
@@ -6015,10 +6124,10 @@
       <c r="D19" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="E19" s="33" t="s">
+      <c r="E19" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="F19" s="36" t="s">
+      <c r="F19" s="24" t="s">
         <v>515</v>
       </c>
       <c r="G19" s="24" t="s">
@@ -6038,8 +6147,11 @@
         <f t="shared" si="1"/>
         <v>3-1</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L19" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="20" t="s">
         <v>253</v>
       </c>
@@ -6049,38 +6161,41 @@
       <c r="C20" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E20" s="32" t="s">
+      <c r="E20" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="F20" s="32" t="s">
+      <c r="F20" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="G20" s="32" t="s">
+      <c r="G20" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="H20" s="32">
+      <c r="H20" s="1">
         <v>8</v>
       </c>
-      <c r="I20" s="32" t="s">
+      <c r="I20" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="J20" s="32" t="str">
+      <c r="J20" s="1" t="str">
         <f t="shared" si="0"/>
         <v>3-4</v>
       </c>
-      <c r="K20" s="32" t="str">
+      <c r="K20" s="1" t="str">
         <f t="shared" si="1"/>
         <v>3-2</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="41" t="s">
+      <c r="L20" s="39">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="32" t="s">
         <v>254</v>
       </c>
-      <c r="B21" s="41" t="s">
+      <c r="B21" s="32" t="s">
         <v>254</v>
       </c>
       <c r="C21" s="24" t="s">
@@ -6089,29 +6204,32 @@
       <c r="D21" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="34" t="s">
+      <c r="E21" s="28" t="s">
         <v>545</v>
       </c>
-      <c r="F21" s="34" t="s">
+      <c r="F21" s="28" t="s">
         <v>515</v>
       </c>
-      <c r="G21" s="34" t="s">
+      <c r="G21" s="28" t="s">
         <v>515</v>
       </c>
-      <c r="H21" s="34"/>
-      <c r="I21" s="34" t="s">
+      <c r="H21" s="28"/>
+      <c r="I21" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="J21" s="34" t="str">
+      <c r="J21" s="28" t="str">
         <f t="shared" si="0"/>
         <v>3-5</v>
       </c>
-      <c r="K21" s="34" t="str">
+      <c r="K21" s="28" t="str">
         <f t="shared" si="1"/>
         <v>3-3</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L21" s="24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="20" t="s">
         <v>255</v>
       </c>
@@ -6121,38 +6239,41 @@
       <c r="C22" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="32" t="s">
+      <c r="D22" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="E22" s="32" t="s">
+      <c r="E22" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="F22" s="32" t="s">
+      <c r="F22" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="G22" s="32" t="s">
+      <c r="G22" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="H22" s="32">
+      <c r="H22" s="1">
         <v>8</v>
       </c>
-      <c r="I22" s="32" t="s">
+      <c r="I22" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="J22" s="32" t="str">
+      <c r="J22" s="1" t="str">
         <f t="shared" si="0"/>
         <v>3-6</v>
       </c>
-      <c r="K22" s="32" t="str">
+      <c r="K22" s="1" t="str">
         <f t="shared" si="1"/>
         <v>3-4</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="41" t="s">
+      <c r="L22" s="39">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="32" t="s">
         <v>256</v>
       </c>
-      <c r="B23" s="41" t="s">
+      <c r="B23" s="32" t="s">
         <v>256</v>
       </c>
       <c r="C23" s="24" t="s">
@@ -6161,10 +6282,10 @@
       <c r="D23" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="E23" s="33" t="s">
+      <c r="E23" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="F23" s="36" t="s">
+      <c r="F23" s="24" t="s">
         <v>515</v>
       </c>
       <c r="G23" s="24" t="s">
@@ -6184,8 +6305,11 @@
         <f t="shared" si="1"/>
         <v>3-5</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L23" s="24">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="20" t="s">
         <v>257</v>
       </c>
@@ -6195,38 +6319,41 @@
       <c r="C24" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D24" s="32" t="s">
+      <c r="D24" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="E24" s="32" t="s">
+      <c r="E24" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="F24" s="32" t="s">
+      <c r="F24" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="G24" s="32" t="s">
+      <c r="G24" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="H24" s="32">
+      <c r="H24" s="1">
         <v>8</v>
       </c>
-      <c r="I24" s="32" t="s">
+      <c r="I24" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="J24" s="32" t="str">
+      <c r="J24" s="1" t="str">
         <f t="shared" si="0"/>
         <v>3-8</v>
       </c>
-      <c r="K24" s="32" t="str">
+      <c r="K24" s="1" t="str">
         <f t="shared" si="1"/>
         <v>3-6</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="41" t="s">
+      <c r="L24" s="39">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="32" t="s">
         <v>258</v>
       </c>
-      <c r="B25" s="41" t="s">
+      <c r="B25" s="32" t="s">
         <v>258</v>
       </c>
       <c r="C25" s="24" t="s">
@@ -6235,29 +6362,32 @@
       <c r="D25" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="E25" s="34" t="s">
+      <c r="E25" s="28" t="s">
         <v>545</v>
       </c>
-      <c r="F25" s="34" t="s">
+      <c r="F25" s="28" t="s">
         <v>515</v>
       </c>
-      <c r="G25" s="34" t="s">
+      <c r="G25" s="28" t="s">
         <v>515</v>
       </c>
-      <c r="H25" s="34"/>
-      <c r="I25" s="34" t="s">
+      <c r="H25" s="28"/>
+      <c r="I25" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="J25" s="34" t="str">
+      <c r="J25" s="28" t="str">
         <f t="shared" si="0"/>
         <v>3-9</v>
       </c>
-      <c r="K25" s="34" t="str">
+      <c r="K25" s="28" t="str">
         <f t="shared" si="1"/>
         <v>3-7</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L25" s="24">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="20" t="s">
         <v>259</v>
       </c>
@@ -6267,38 +6397,41 @@
       <c r="C26" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="D26" s="32" t="s">
+      <c r="D26" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E26" s="32" t="s">
+      <c r="E26" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="F26" s="32" t="s">
+      <c r="F26" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="G26" s="32" t="s">
+      <c r="G26" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="H26" s="32">
+      <c r="H26" s="1">
         <v>9</v>
       </c>
-      <c r="I26" s="32" t="s">
+      <c r="I26" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="J26" s="32" t="str">
+      <c r="J26" s="1" t="str">
         <f>A27</f>
         <v>3-10</v>
       </c>
-      <c r="K26" s="32" t="str">
+      <c r="K26" s="1" t="str">
         <f t="shared" si="1"/>
         <v>3-8</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="41" t="s">
+      <c r="L26" s="40">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="32" t="s">
         <v>260</v>
       </c>
-      <c r="B27" s="41" t="s">
+      <c r="B27" s="32" t="s">
         <v>260</v>
       </c>
       <c r="C27" s="24" t="s">
@@ -6307,10 +6440,10 @@
       <c r="D27" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="E27" s="33" t="s">
+      <c r="E27" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="F27" s="36" t="s">
+      <c r="F27" s="24" t="s">
         <v>450</v>
       </c>
       <c r="G27" s="24" t="s">
@@ -6330,8 +6463,11 @@
         <f t="shared" si="1"/>
         <v>3-9</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L27" s="24">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="20" t="s">
         <v>261</v>
       </c>
@@ -6341,36 +6477,39 @@
       <c r="C28" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="D28" s="32" t="s">
+      <c r="D28" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E28" s="34" t="s">
+      <c r="E28" s="28" t="s">
         <v>545</v>
       </c>
-      <c r="F28" s="34" t="s">
+      <c r="F28" s="28" t="s">
         <v>515</v>
       </c>
-      <c r="G28" s="34" t="s">
+      <c r="G28" s="28" t="s">
         <v>515</v>
       </c>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34" t="s">
+      <c r="H28" s="28"/>
+      <c r="I28" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="J28" s="34" t="str">
+      <c r="J28" s="28" t="str">
         <f t="shared" si="0"/>
         <v>3-12</v>
       </c>
-      <c r="K28" s="34" t="str">
+      <c r="K28" s="28" t="str">
         <f t="shared" si="1"/>
         <v>3-10</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="41" t="s">
+      <c r="L28" s="40">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="32" t="s">
         <v>262</v>
       </c>
-      <c r="B29" s="41" t="s">
+      <c r="B29" s="32" t="s">
         <v>262</v>
       </c>
       <c r="C29" s="24" t="s">
@@ -6379,16 +6518,16 @@
       <c r="D29" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="E29" s="33" t="s">
+      <c r="E29" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="F29" s="33" t="s">
+      <c r="F29" s="2" t="s">
         <v>451</v>
       </c>
       <c r="G29" s="24" t="s">
         <v>514</v>
       </c>
-      <c r="H29" s="33">
+      <c r="H29" s="2">
         <v>9</v>
       </c>
       <c r="I29" s="24" t="s">
@@ -6402,8 +6541,11 @@
         <f t="shared" si="1"/>
         <v>3-11</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L29" s="24">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="20" t="s">
         <v>267</v>
       </c>
@@ -6413,36 +6555,39 @@
       <c r="C30" s="6" t="s">
         <v>409</v>
       </c>
-      <c r="D30" s="32" t="s">
+      <c r="D30" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="E30" s="34" t="s">
+      <c r="E30" s="28" t="s">
         <v>545</v>
       </c>
-      <c r="F30" s="34" t="s">
+      <c r="F30" s="28" t="s">
         <v>515</v>
       </c>
-      <c r="G30" s="34" t="s">
+      <c r="G30" s="28" t="s">
         <v>515</v>
       </c>
-      <c r="H30" s="34"/>
-      <c r="I30" s="34" t="s">
+      <c r="H30" s="28"/>
+      <c r="I30" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="J30" s="34" t="str">
+      <c r="J30" s="28" t="str">
         <f t="shared" si="0"/>
         <v>4-2</v>
       </c>
-      <c r="K30" s="34" t="str">
+      <c r="K30" s="28" t="str">
         <f t="shared" si="1"/>
         <v>3-12</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="41" t="s">
+      <c r="L30" s="40">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="32" t="s">
         <v>268</v>
       </c>
-      <c r="B31" s="41" t="s">
+      <c r="B31" s="32" t="s">
         <v>268</v>
       </c>
       <c r="C31" s="24" t="s">
@@ -6451,10 +6596,10 @@
       <c r="D31" s="24" t="s">
         <v>298</v>
       </c>
-      <c r="E31" s="33" t="s">
+      <c r="E31" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="F31" s="36" t="s">
+      <c r="F31" s="24" t="s">
         <v>515</v>
       </c>
       <c r="G31" s="24" t="s">
@@ -6474,8 +6619,11 @@
         <f t="shared" si="1"/>
         <v>4-1</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L31" s="24">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="20" t="s">
         <v>269</v>
       </c>
@@ -6485,38 +6633,39 @@
       <c r="C32" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D32" s="32" t="s">
+      <c r="D32" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E32" s="32" t="s">
+      <c r="E32" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="F32" s="32" t="s">
+      <c r="F32" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="G32" s="32" t="s">
+      <c r="G32" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="H32" s="32">
+      <c r="H32" s="1">
         <v>10</v>
       </c>
-      <c r="I32" s="32" t="s">
+      <c r="I32" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="J32" s="32" t="str">
+      <c r="J32" s="1" t="str">
         <f t="shared" si="0"/>
         <v>4-4A</v>
       </c>
-      <c r="K32" s="32" t="str">
+      <c r="K32" s="1" t="str">
         <f t="shared" si="1"/>
         <v>4-2</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="41" t="s">
+      <c r="L32" s="36"/>
+    </row>
+    <row r="33" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="32" t="s">
         <v>270</v>
       </c>
-      <c r="B33" s="41" t="s">
+      <c r="B33" s="32" t="s">
         <v>270</v>
       </c>
       <c r="C33" s="24" t="s">
@@ -6525,10 +6674,10 @@
       <c r="D33" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="E33" s="33" t="s">
+      <c r="E33" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="F33" s="36" t="s">
+      <c r="F33" s="24" t="s">
         <v>452</v>
       </c>
       <c r="G33" s="24" t="s">
@@ -6549,7 +6698,7 @@
         <v>4-3A</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="20" t="s">
         <v>271</v>
       </c>
@@ -6559,38 +6708,39 @@
       <c r="C34" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="D34" s="32" t="s">
+      <c r="D34" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E34" s="32" t="s">
+      <c r="E34" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="F34" s="32" t="s">
+      <c r="F34" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="G34" s="32" t="s">
+      <c r="G34" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="H34" s="32">
+      <c r="H34" s="1">
         <v>10</v>
       </c>
-      <c r="I34" s="32" t="s">
+      <c r="I34" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="J34" s="32" t="str">
+      <c r="J34" s="1" t="str">
         <f t="shared" si="0"/>
         <v>4-6A</v>
       </c>
-      <c r="K34" s="32" t="str">
+      <c r="K34" s="1" t="str">
         <f t="shared" si="1"/>
         <v>4-4A</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="41" t="s">
+      <c r="L34" s="36"/>
+    </row>
+    <row r="35" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="32" t="s">
         <v>272</v>
       </c>
-      <c r="B35" s="41" t="s">
+      <c r="B35" s="32" t="s">
         <v>272</v>
       </c>
       <c r="C35" s="24" t="s">
@@ -6599,10 +6749,10 @@
       <c r="D35" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="E35" s="33" t="s">
+      <c r="E35" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="F35" s="36" t="s">
+      <c r="F35" s="24" t="s">
         <v>452</v>
       </c>
       <c r="G35" s="24" t="s">
@@ -6623,7 +6773,7 @@
         <v>4-5A</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="20" t="s">
         <v>273</v>
       </c>
@@ -6633,38 +6783,39 @@
       <c r="C36" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="D36" s="32" t="s">
+      <c r="D36" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E36" s="32" t="s">
+      <c r="E36" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="F36" s="32" t="s">
+      <c r="F36" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="G36" s="32" t="s">
+      <c r="G36" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="H36" s="32">
+      <c r="H36" s="1">
         <v>10</v>
       </c>
-      <c r="I36" s="32" t="s">
+      <c r="I36" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="J36" s="32" t="str">
+      <c r="J36" s="1" t="str">
         <f t="shared" si="0"/>
         <v>4-8A</v>
       </c>
-      <c r="K36" s="32" t="str">
+      <c r="K36" s="1" t="str">
         <f t="shared" si="1"/>
         <v>4-6A</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="41" t="s">
+      <c r="L36" s="36"/>
+    </row>
+    <row r="37" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="32" t="s">
         <v>274</v>
       </c>
-      <c r="B37" s="41" t="s">
+      <c r="B37" s="32" t="s">
         <v>274</v>
       </c>
       <c r="C37" s="7" t="s">
@@ -6673,13 +6824,13 @@
       <c r="D37" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="E37" s="33" t="s">
+      <c r="E37" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="F37" s="33" t="s">
+      <c r="F37" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="G37" s="33" t="s">
+      <c r="G37" s="2" t="s">
         <v>472</v>
       </c>
       <c r="H37" s="24">
@@ -6697,7 +6848,7 @@
         <v>4-7A</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
         <v>275</v>
       </c>
@@ -6707,38 +6858,39 @@
       <c r="C38" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D38" s="32" t="s">
+      <c r="D38" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E38" s="32" t="s">
+      <c r="E38" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="F38" s="32" t="s">
+      <c r="F38" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="G38" s="32" t="s">
+      <c r="G38" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="H38" s="32">
+      <c r="H38" s="1">
         <v>10</v>
       </c>
-      <c r="I38" s="32" t="s">
+      <c r="I38" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="J38" s="32" t="str">
+      <c r="J38" s="1" t="str">
         <f t="shared" si="0"/>
         <v>4-4B</v>
       </c>
-      <c r="K38" s="32" t="str">
+      <c r="K38" s="1" t="str">
         <f t="shared" si="1"/>
         <v>4-8A</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="41" t="s">
+      <c r="L38" s="36"/>
+    </row>
+    <row r="39" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="32" t="s">
         <v>276</v>
       </c>
-      <c r="B39" s="41" t="s">
+      <c r="B39" s="32" t="s">
         <v>276</v>
       </c>
       <c r="C39" s="24" t="s">
@@ -6747,10 +6899,10 @@
       <c r="D39" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="E39" s="33" t="s">
+      <c r="E39" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="F39" s="36" t="s">
+      <c r="F39" s="24" t="s">
         <v>452</v>
       </c>
       <c r="G39" s="24" t="s">
@@ -6771,48 +6923,49 @@
         <v>4-3B</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="20" t="s">
         <v>277</v>
       </c>
       <c r="B40" s="20" t="s">
         <v>277</v>
       </c>
-      <c r="C40" s="32" t="s">
+      <c r="C40" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D40" s="32" t="s">
+      <c r="D40" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E40" s="32" t="s">
+      <c r="E40" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="F40" s="32" t="s">
+      <c r="F40" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="G40" s="32" t="s">
+      <c r="G40" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="H40" s="32">
+      <c r="H40" s="1">
         <v>10</v>
       </c>
-      <c r="I40" s="32" t="s">
+      <c r="I40" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="J40" s="32" t="str">
+      <c r="J40" s="1" t="str">
         <f t="shared" si="0"/>
         <v>4-6B</v>
       </c>
-      <c r="K40" s="32" t="str">
+      <c r="K40" s="1" t="str">
         <f t="shared" si="1"/>
         <v>4-4B</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="41" t="s">
+      <c r="L40" s="36"/>
+    </row>
+    <row r="41" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="32" t="s">
         <v>278</v>
       </c>
-      <c r="B41" s="41" t="s">
+      <c r="B41" s="32" t="s">
         <v>278</v>
       </c>
       <c r="C41" s="24" t="s">
@@ -6821,10 +6974,10 @@
       <c r="D41" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="E41" s="33" t="s">
+      <c r="E41" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="F41" s="36" t="s">
+      <c r="F41" s="24" t="s">
         <v>452</v>
       </c>
       <c r="G41" s="24" t="s">
@@ -6845,48 +6998,49 @@
         <v>4-5B</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="20" t="s">
         <v>279</v>
       </c>
       <c r="B42" s="20" t="s">
         <v>279</v>
       </c>
-      <c r="C42" s="32" t="s">
+      <c r="C42" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D42" s="32" t="s">
+      <c r="D42" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E42" s="32" t="s">
+      <c r="E42" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="F42" s="32" t="s">
+      <c r="F42" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="G42" s="32" t="s">
+      <c r="G42" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="H42" s="32">
+      <c r="H42" s="1">
         <v>10</v>
       </c>
-      <c r="I42" s="32" t="s">
+      <c r="I42" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="J42" s="32" t="str">
+      <c r="J42" s="1" t="str">
         <f t="shared" si="0"/>
         <v>4-8B</v>
       </c>
-      <c r="K42" s="32" t="str">
+      <c r="K42" s="1" t="str">
         <f t="shared" si="1"/>
         <v>4-6B</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="41" t="s">
+      <c r="L42" s="36"/>
+    </row>
+    <row r="43" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="32" t="s">
         <v>280</v>
       </c>
-      <c r="B43" s="41" t="s">
+      <c r="B43" s="32" t="s">
         <v>280</v>
       </c>
       <c r="C43" s="24" t="s">
@@ -6895,10 +7049,10 @@
       <c r="D43" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="E43" s="33" t="s">
+      <c r="E43" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="F43" s="33" t="s">
+      <c r="F43" s="2" t="s">
         <v>517</v>
       </c>
       <c r="G43" s="24" t="s">
@@ -6910,22 +7064,22 @@
       <c r="I43" s="24" t="s">
         <v>405</v>
       </c>
-      <c r="J43" s="43"/>
+      <c r="J43" s="34"/>
       <c r="K43" s="24" t="str">
         <f>B42</f>
         <v>4-7B</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="32"/>
-      <c r="B44" s="32"/>
-      <c r="C44" s="32"/>
-      <c r="D44" s="32"/>
-      <c r="E44" s="32"/>
-      <c r="F44" s="32"/>
-      <c r="G44" s="32"/>
-      <c r="H44" s="32"/>
-      <c r="I44" s="32"/>
+    <row r="44" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6937,24 +7091,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63585447-8EF3-4F6F-B5BC-B3B0F6A0BFCE}">
   <dimension ref="A1:O8"/>
-  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="13" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="2" width="10.58203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="10.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.21875" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.75" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="34.9140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.88671875" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="44.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="37.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="47" style="3" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17" style="3" customWidth="1"/>
-    <col min="11" max="11" width="16.58203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.08203125" style="3" customWidth="1"/>
-    <col min="13" max="13" width="16.58203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.9140625" style="3"/>
+    <col min="11" max="11" width="16.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.109375" style="3" customWidth="1"/>
+    <col min="13" max="13" width="16.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -6997,7 +7151,7 @@
       <c r="N1" s="9"/>
       <c r="O1" s="9"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A2" s="23" t="s">
         <v>3</v>
       </c>
@@ -7007,31 +7161,31 @@
       <c r="C2" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="D2" s="28">
+      <c r="D2" s="15">
         <v>1</v>
       </c>
       <c r="E2" s="15">
         <v>5</v>
       </c>
-      <c r="F2" s="28">
-        <v>0</v>
-      </c>
-      <c r="G2" s="35">
-        <v>0</v>
-      </c>
-      <c r="H2" s="28">
-        <v>0</v>
-      </c>
-      <c r="I2" s="28">
+      <c r="F2" s="15">
+        <v>0</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0</v>
+      </c>
+      <c r="H2" s="15">
+        <v>0</v>
+      </c>
+      <c r="I2" s="15">
         <v>1</v>
       </c>
-      <c r="J2" s="35">
+      <c r="J2" s="15">
         <v>1</v>
       </c>
       <c r="K2" s="15">
         <v>0.9</v>
       </c>
-      <c r="L2" s="35">
+      <c r="L2" s="15">
         <v>10</v>
       </c>
       <c r="M2" s="15">
@@ -7040,7 +7194,7 @@
       <c r="N2" s="15"/>
       <c r="O2" s="15"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A3" s="14" t="s">
         <v>222</v>
       </c>
@@ -7050,20 +7204,20 @@
       <c r="C3" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="D3" s="29">
+      <c r="D3" s="26">
         <v>0.15</v>
       </c>
       <c r="E3" s="26">
         <v>4</v>
       </c>
-      <c r="F3" s="29">
+      <c r="F3" s="26">
         <v>0.1</v>
       </c>
-      <c r="G3" s="39"/>
-      <c r="H3" s="29">
+      <c r="G3" s="30"/>
+      <c r="H3" s="26">
         <v>0.1</v>
       </c>
-      <c r="I3" s="39"/>
+      <c r="I3" s="30"/>
       <c r="J3" s="26">
         <v>0.8</v>
       </c>
@@ -7079,7 +7233,7 @@
       <c r="N3" s="26"/>
       <c r="O3" s="26"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A4" s="25" t="s">
         <v>223</v>
       </c>
@@ -7089,31 +7243,31 @@
       <c r="C4" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="15">
         <v>1</v>
       </c>
       <c r="E4" s="15">
         <v>4</v>
       </c>
-      <c r="F4" s="28">
-        <v>0</v>
-      </c>
-      <c r="G4" s="28">
+      <c r="F4" s="15">
+        <v>0</v>
+      </c>
+      <c r="G4" s="15">
         <v>-1</v>
       </c>
-      <c r="H4" s="28">
+      <c r="H4" s="15">
         <v>-0.1</v>
       </c>
-      <c r="I4" s="28">
+      <c r="I4" s="15">
         <v>1</v>
       </c>
-      <c r="J4" s="35">
+      <c r="J4" s="15">
         <v>1</v>
       </c>
       <c r="K4" s="15">
         <v>0.9</v>
       </c>
-      <c r="L4" s="35">
+      <c r="L4" s="15">
         <v>8</v>
       </c>
       <c r="M4" s="15">
@@ -7122,7 +7276,7 @@
       <c r="N4" s="15"/>
       <c r="O4" s="15"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
         <v>224</v>
       </c>
@@ -7132,22 +7286,22 @@
       <c r="C5" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="3">
         <v>0.3</v>
       </c>
       <c r="E5" s="3">
         <v>3</v>
       </c>
-      <c r="F5" s="30">
-        <v>0</v>
-      </c>
-      <c r="G5" s="30">
-        <v>0</v>
-      </c>
-      <c r="H5" s="30">
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
         <v>0.2</v>
       </c>
-      <c r="I5" s="30">
+      <c r="I5" s="3">
         <v>-1</v>
       </c>
       <c r="J5" s="3">
@@ -7163,7 +7317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
         <v>225</v>
       </c>
@@ -7173,31 +7327,31 @@
       <c r="C6" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="15">
         <v>0.95</v>
       </c>
       <c r="E6" s="15">
         <v>7</v>
       </c>
-      <c r="F6" s="28">
-        <v>0</v>
-      </c>
-      <c r="G6" s="28">
+      <c r="F6" s="15">
+        <v>0</v>
+      </c>
+      <c r="G6" s="15">
         <v>1</v>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="15">
         <v>-0.1</v>
       </c>
-      <c r="I6" s="28">
+      <c r="I6" s="15">
         <v>1</v>
       </c>
-      <c r="J6" s="35">
+      <c r="J6" s="15">
         <v>0.95</v>
       </c>
       <c r="K6" s="15">
         <v>0.1</v>
       </c>
-      <c r="L6" s="35">
+      <c r="L6" s="15">
         <v>10</v>
       </c>
       <c r="M6" s="15">
@@ -7206,7 +7360,7 @@
       <c r="N6" s="15"/>
       <c r="O6" s="15"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A7" s="3" t="s">
         <v>226</v>
       </c>
@@ -7216,22 +7370,22 @@
       <c r="C7" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="3">
         <v>1</v>
       </c>
       <c r="E7" s="3">
         <v>5</v>
       </c>
-      <c r="F7" s="30">
-        <v>0</v>
-      </c>
-      <c r="G7" s="30">
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
         <v>1</v>
       </c>
-      <c r="H7" s="30">
-        <v>0</v>
-      </c>
-      <c r="I7" s="30">
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
         <v>0</v>
       </c>
       <c r="J7" s="3">
@@ -7247,7 +7401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A8" s="23"/>
       <c r="B8" s="25"/>
       <c r="C8" s="1"/>
@@ -7274,18 +7428,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BB5D973-7E16-4329-8813-6C2FD7D5209C}">
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="13" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="2" width="9.58203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.9140625" style="12"/>
+    <col min="1" max="2" width="9.5546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="12"/>
     <col min="4" max="4" width="30" style="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="33.6640625" style="12" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19" style="12" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="26.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.9140625" style="12"/>
+    <col min="9" max="16384" width="8.88671875" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -7312,7 +7466,7 @@
       </c>
       <c r="I1" s="9"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A2" s="23" t="s">
         <v>8</v>
       </c>
@@ -7322,7 +7476,7 @@
       <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="32">
+      <c r="D2" s="1">
         <v>7</v>
       </c>
       <c r="E2" s="15">
@@ -7339,7 +7493,7 @@
       </c>
       <c r="I2" s="15"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A3" s="13" t="s">
         <v>227</v>
       </c>
@@ -7349,7 +7503,7 @@
       <c r="C3" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D3" s="33">
+      <c r="D3" s="2">
         <v>3</v>
       </c>
       <c r="E3" s="26">
@@ -7366,7 +7520,7 @@
       </c>
       <c r="I3" s="26"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A4" s="23" t="s">
         <v>228</v>
       </c>
@@ -7376,7 +7530,7 @@
       <c r="C4" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="D4" s="32">
+      <c r="D4" s="1">
         <v>0</v>
       </c>
       <c r="E4" s="15">

--- a/Src/Assets/Common/Tables/Tables/Levels.xlsx
+++ b/Src/Assets/Common/Tables/Tables/Levels.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CCA\Src\Assets\Common\Tables\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33A18087-E343-4034-8079-7F663B719642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74CEE958-6A41-4350-972D-B6ABC1C7DC8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="2" r:id="rId1"/>
@@ -6973,7 +6973,7 @@
     <col min="4" max="4" width="29.25" style="16" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.33203125" style="16" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="174.08203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.58203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.6640625" style="16" customWidth="1"/>
     <col min="8" max="8" width="12.58203125" style="16" customWidth="1"/>
     <col min="9" max="9" width="34.75" style="16" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="50.08203125" style="16" bestFit="1" customWidth="1"/>

--- a/Src/Assets/Common/Tables/Tables/Levels.xlsx
+++ b/Src/Assets/Common/Tables/Tables/Levels.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CCA\Src\Assets\Common\Tables\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74CEE958-6A41-4350-972D-B6ABC1C7DC8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6867075D-A563-474B-A0D9-C92C654A91BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="490">
   <si>
     <t>Key</t>
   </si>
@@ -132,12 +132,6 @@
     <t>PlayerInitialResource</t>
   </si>
   <si>
-    <t>NextLevel</t>
-  </si>
-  <si>
-    <t>PreviousLevel</t>
-  </si>
-  <si>
     <t>1-1</t>
   </si>
   <si>
@@ -476,10 +470,6 @@
   </si>
   <si>
     <t>Shadow_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>影</t>
@@ -1982,6 +1972,14 @@
   <si>
     <t>["sword","ghost_sever"]</t>
     <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>NextLevel</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreviousLevel</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2813,22 +2811,22 @@
         <v>3</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
@@ -2843,7 +2841,7 @@
         <v>15</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D2" s="7">
         <v>4</v>
@@ -2876,7 +2874,7 @@
         <v>21</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D3" s="10">
         <v>2</v>
@@ -2903,13 +2901,13 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="D4" s="7">
         <v>2</v>
@@ -2942,7 +2940,7 @@
         <v>14</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D5" s="11">
         <v>2</v>
@@ -2971,7 +2969,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D6" s="7">
         <v>7</v>
@@ -3004,7 +3002,7 @@
         <v>10</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D7" s="11">
         <v>5</v>
@@ -3072,31 +3070,31 @@
         <v>3</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="I1" s="3"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D2" s="6">
         <v>7</v>
@@ -3105,7 +3103,7 @@
         <v>100</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G2" s="7">
         <v>0.7</v>
@@ -3117,13 +3115,13 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D3" s="9">
         <v>3</v>
@@ -3132,7 +3130,7 @@
         <v>7</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G3" s="10">
         <v>0.4</v>
@@ -3144,13 +3142,13 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D4" s="6">
         <v>0</v>
@@ -3159,7 +3157,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G4" s="7">
         <v>0.3</v>
@@ -3209,13 +3207,13 @@
         <v>2</v>
       </c>
       <c r="E1" s="36" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="F1" s="22" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="36" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="H1" s="22" t="s">
         <v>8</v>
@@ -3233,10 +3231,10 @@
         <v>7</v>
       </c>
       <c r="M1" s="36" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N1" s="36" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O1" s="22"/>
       <c r="P1" s="22"/>
@@ -3244,27 +3242,31 @@
     </row>
     <row r="2" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B2" s="4" t="str">
         <f>A2</f>
         <v>Toy Grunt</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F2" s="26" t="b">
         <v>0</v>
       </c>
       <c r="G2" s="26"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="26"/>
+      <c r="H2" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="I2" s="26" t="s">
+        <v>11</v>
+      </c>
       <c r="J2" s="6">
         <v>2</v>
       </c>
@@ -3273,13 +3275,13 @@
         <v>2</v>
       </c>
       <c r="L2" s="26" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M2" s="26" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N2" s="26" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
@@ -3287,23 +3289,29 @@
     </row>
     <row r="3" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B3" s="27" t="str">
         <f t="shared" ref="B3:B21" si="0">A3</f>
         <v>Toy Warrior</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F3" s="16" t="b">
         <v>0</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>11</v>
       </c>
       <c r="J3" s="11">
         <v>2</v>
@@ -3316,35 +3324,39 @@
         <v>12</v>
       </c>
       <c r="M3" s="16" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B4" s="28" t="str">
         <f t="shared" si="0"/>
         <v>Toy Guardian</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F4" s="6" t="b">
         <v>0</v>
       </c>
       <c r="G4" s="6"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
+      <c r="H4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>11</v>
+      </c>
       <c r="J4" s="7">
         <v>2</v>
       </c>
@@ -3356,10 +3368,10 @@
         <v>12</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
@@ -3367,23 +3379,29 @@
     </row>
     <row r="5" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="29" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B5" s="29" t="str">
         <f t="shared" si="0"/>
         <v>Toy Minion</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D5" s="16" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F5" s="16" t="b">
         <v>0</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>11</v>
       </c>
       <c r="J5" s="11">
         <v>1</v>
@@ -3396,35 +3414,39 @@
         <v>12</v>
       </c>
       <c r="M5" s="16" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="30" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B6" s="30" t="str">
         <f t="shared" si="0"/>
         <v>Toy Gentleman</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>14</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F6" s="61" t="b">
         <v>1</v>
       </c>
       <c r="G6" s="6"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
+      <c r="H6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>11</v>
+      </c>
       <c r="J6" s="7">
         <v>4</v>
       </c>
@@ -3436,10 +3458,10 @@
         <v>12</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N6" s="58" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
@@ -3447,26 +3469,29 @@
     </row>
     <row r="7" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="29" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B7" s="29" t="str">
         <f t="shared" si="0"/>
         <v>Toy Factory</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D7" s="16" t="s">
         <v>15</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F7" s="16" t="b">
         <v>0</v>
       </c>
       <c r="H7" s="29" t="s">
-        <v>476</v>
+        <v>473</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>11</v>
       </c>
       <c r="J7" s="11">
         <v>7</v>
@@ -3479,37 +3504,39 @@
         <v>12</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N7" s="29" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="33" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B8" s="33" t="str">
         <f t="shared" si="0"/>
         <v>Swordsman of Faith</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F8" s="33" t="b">
         <v>0</v>
       </c>
       <c r="G8" s="33"/>
       <c r="H8" s="33" t="s">
-        <v>240</v>
-      </c>
-      <c r="I8" s="33"/>
+        <v>237</v>
+      </c>
+      <c r="I8" s="33" t="s">
+        <v>11</v>
+      </c>
       <c r="J8" s="33">
         <v>4</v>
       </c>
@@ -3518,13 +3545,13 @@
         <v>4</v>
       </c>
       <c r="L8" s="33" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M8" s="33" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N8" s="33" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="O8" s="33"/>
       <c r="P8" s="33"/>
@@ -3545,7 +3572,7 @@
         <v>13</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F9" s="11" t="b">
         <v>0</v>
@@ -3554,6 +3581,9 @@
       <c r="H9" s="11" t="s">
         <v>16</v>
       </c>
+      <c r="I9" s="11" t="s">
+        <v>11</v>
+      </c>
       <c r="J9" s="11">
         <v>1</v>
       </c>
@@ -3565,10 +3595,10 @@
         <v>12</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N9" s="11" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3583,10 +3613,10 @@
         <v>20</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F10" s="32" t="b">
         <v>0</v>
@@ -3595,7 +3625,9 @@
       <c r="H10" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="I10" s="32"/>
+      <c r="I10" s="32" t="s">
+        <v>11</v>
+      </c>
       <c r="J10" s="32">
         <v>3</v>
       </c>
@@ -3607,10 +3639,10 @@
         <v>12</v>
       </c>
       <c r="M10" s="32" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N10" s="32" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="O10" s="32"/>
       <c r="P10" s="32"/>
@@ -3618,20 +3650,20 @@
     </row>
     <row r="11" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B11" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Furious Skunk</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F11" s="11" t="b">
         <v>0</v>
@@ -3640,6 +3672,9 @@
       <c r="H11" s="11" t="s">
         <v>16</v>
       </c>
+      <c r="I11" s="11" t="s">
+        <v>11</v>
+      </c>
       <c r="J11" s="11">
         <v>5</v>
       </c>
@@ -3651,15 +3686,15 @@
         <v>12</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N11" s="11" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="32" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B12" s="32" t="str">
         <f t="shared" si="0"/>
@@ -3672,7 +3707,7 @@
         <v>21</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F12" s="32" t="b">
         <v>0</v>
@@ -3681,7 +3716,9 @@
       <c r="H12" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="I12" s="32"/>
+      <c r="I12" s="32" t="s">
+        <v>11</v>
+      </c>
       <c r="J12" s="32">
         <v>2</v>
       </c>
@@ -3693,10 +3730,10 @@
         <v>12</v>
       </c>
       <c r="M12" s="32" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N12" s="32" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="O12" s="32"/>
       <c r="P12" s="32"/>
@@ -3717,13 +3754,19 @@
         <v>21</v>
       </c>
       <c r="E13" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="F13" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="F13" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>239</v>
+      <c r="H13" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>11</v>
       </c>
       <c r="J13" s="11">
         <v>7</v>
@@ -3736,35 +3779,39 @@
         <v>12</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N13" s="29" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="33" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B14" s="33" t="str">
         <f t="shared" si="0"/>
         <v>Shadow of Void</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F14" s="33" t="b">
         <v>0</v>
       </c>
       <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
+      <c r="H14" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" s="33" t="s">
+        <v>11</v>
+      </c>
       <c r="J14" s="33">
         <v>6</v>
       </c>
@@ -3773,13 +3820,13 @@
         <v>6</v>
       </c>
       <c r="L14" s="33" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M14" s="33" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N14" s="33" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="O14" s="33"/>
       <c r="P14" s="33"/>
@@ -3787,29 +3834,32 @@
     </row>
     <row r="15" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B15" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Void Beast</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E15" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="F15" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="F15" s="11" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>238</v>
-      </c>
       <c r="H15" s="11" t="s">
-        <v>135</v>
+        <v>11</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>11</v>
       </c>
       <c r="J15" s="11">
         <v>1</v>
@@ -3819,40 +3869,44 @@
         <v>1</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N15" s="29" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="32" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B16" s="32" t="str">
         <f t="shared" si="0"/>
         <v>Chronos Hand</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F16" s="32" t="b">
         <v>0</v>
       </c>
       <c r="G16" s="32" t="s">
-        <v>240</v>
-      </c>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
+        <v>237</v>
+      </c>
+      <c r="H16" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="I16" s="32" t="s">
+        <v>11</v>
+      </c>
       <c r="J16" s="32">
         <v>3</v>
       </c>
@@ -3864,10 +3918,10 @@
         <v>12</v>
       </c>
       <c r="M16" s="32" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N16" s="33" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="O16" s="32"/>
       <c r="P16" s="32"/>
@@ -3875,26 +3929,32 @@
     </row>
     <row r="17" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B17" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Mnemosyne Hand</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F17" s="11" t="b">
         <v>0</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>238</v>
+        <v>235</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>11</v>
       </c>
       <c r="J17" s="40">
         <v>3</v>
@@ -3907,45 +3967,49 @@
         <v>12</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N17" s="29" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="32" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B18" s="32" t="str">
         <f t="shared" si="0"/>
         <v>Entity of Will</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F18" s="54" t="b">
         <v>1</v>
       </c>
       <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="50"/>
+      <c r="H18" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="I18" s="50" t="s">
+        <v>11</v>
+      </c>
       <c r="J18" s="49"/>
       <c r="K18" s="48"/>
       <c r="L18" s="47" t="s">
         <v>12</v>
       </c>
       <c r="M18" s="32" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N18" s="33" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="O18" s="32"/>
       <c r="P18" s="32"/>
@@ -3960,20 +4024,23 @@
         <v>Dagger of Void</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F19" s="11" t="b">
         <v>0</v>
       </c>
       <c r="G19" s="11"/>
       <c r="H19" s="11" t="s">
-        <v>240</v>
+        <v>237</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>11</v>
       </c>
       <c r="J19" s="11">
         <v>3</v>
@@ -3986,28 +4053,28 @@
         <v>12</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N19" s="11" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="32" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B20" s="32" t="str">
         <f t="shared" si="0"/>
         <v>Sword of Shadow</v>
       </c>
       <c r="C20" s="32" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D20" s="32" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F20" s="32" t="b">
         <v>0</v>
@@ -4017,7 +4084,7 @@
         <v>16</v>
       </c>
       <c r="I20" s="33" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="J20" s="32">
         <v>2</v>
@@ -4027,13 +4094,13 @@
         <v>2</v>
       </c>
       <c r="L20" s="33" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="M20" s="32" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N20" s="33" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="O20" s="32"/>
       <c r="P20" s="32"/>
@@ -4041,26 +4108,32 @@
     </row>
     <row r="21" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B21" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Stronghold Chieftain</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F21" s="29" t="b">
         <v>0</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>490</v>
+        <v>487</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>11</v>
       </c>
       <c r="J21" s="11">
         <v>16</v>
@@ -4070,40 +4143,44 @@
         <v>16</v>
       </c>
       <c r="L21" s="27" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="M21" s="16" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N21" s="29" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="34" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B22" s="34" t="str">
         <f>A22</f>
         <v>Arbiter of Divine</v>
       </c>
       <c r="C22" s="34" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D22" s="34" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E22" s="34" t="s">
+        <v>233</v>
+      </c>
+      <c r="F22" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="34" t="s">
         <v>236</v>
       </c>
-      <c r="F22" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" s="34" t="s">
-        <v>239</v>
-      </c>
-      <c r="H22" s="34"/>
-      <c r="I22" s="34"/>
+      <c r="H22" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="I22" s="34" t="s">
+        <v>11</v>
+      </c>
       <c r="J22" s="34">
         <v>5</v>
       </c>
@@ -4115,10 +4192,10 @@
         <v>12</v>
       </c>
       <c r="M22" s="34" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N22" s="53" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="O22" s="34"/>
       <c r="P22" s="34"/>
@@ -4126,29 +4203,33 @@
     </row>
     <row r="23" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B23" s="29" t="str">
         <f t="shared" ref="B23:B81" si="2">A23</f>
         <v>Judge of Divine</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D23" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E23" s="29" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F23" s="29" t="b">
         <v>0</v>
       </c>
       <c r="G23" s="29" t="s">
-        <v>240</v>
-      </c>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
+        <v>237</v>
+      </c>
+      <c r="H23" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="I23" s="29" t="s">
+        <v>11</v>
+      </c>
       <c r="J23" s="29">
         <v>6</v>
       </c>
@@ -4157,13 +4238,13 @@
         <v>6</v>
       </c>
       <c r="L23" s="29" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M23" s="29" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N23" s="29" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="O23" s="29"/>
       <c r="P23" s="29"/>
@@ -4171,29 +4252,33 @@
     </row>
     <row r="24" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="34" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B24" s="34" t="str">
         <f t="shared" si="2"/>
         <v>Butaro</v>
       </c>
       <c r="C24" s="34" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D24" s="34" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E24" s="34" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F24" s="34" t="b">
         <v>0</v>
       </c>
       <c r="G24" s="34" t="s">
-        <v>239</v>
-      </c>
-      <c r="H24" s="34"/>
-      <c r="I24" s="34"/>
+        <v>236</v>
+      </c>
+      <c r="H24" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="I24" s="34" t="s">
+        <v>11</v>
+      </c>
       <c r="J24" s="34">
         <v>6</v>
       </c>
@@ -4202,13 +4287,13 @@
         <v>6</v>
       </c>
       <c r="L24" s="34" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M24" s="34" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N24" s="34" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="O24" s="34"/>
       <c r="P24" s="34"/>
@@ -4216,27 +4301,31 @@
     </row>
     <row r="25" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B25" s="29" t="str">
         <f t="shared" si="2"/>
         <v>Huntaro</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D25" s="29" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E25" s="29" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F25" s="29" t="b">
         <v>0</v>
       </c>
       <c r="G25" s="29"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="29"/>
+      <c r="H25" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="I25" s="29" t="s">
+        <v>11</v>
+      </c>
       <c r="J25" s="29">
         <v>3</v>
       </c>
@@ -4245,13 +4334,13 @@
         <v>3</v>
       </c>
       <c r="L25" s="29" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M25" s="29" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N25" s="29" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="O25" s="29"/>
       <c r="P25" s="29"/>
@@ -4259,29 +4348,31 @@
     </row>
     <row r="26" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="34" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B26" s="34" t="str">
         <f t="shared" si="2"/>
         <v>Weasel Bandit</v>
       </c>
       <c r="C26" s="34" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D26" s="34" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E26" s="34" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F26" s="34" t="b">
         <v>0</v>
       </c>
       <c r="G26" s="34"/>
       <c r="H26" s="34" t="s">
-        <v>240</v>
-      </c>
-      <c r="I26" s="34"/>
+        <v>237</v>
+      </c>
+      <c r="I26" s="34" t="s">
+        <v>11</v>
+      </c>
       <c r="J26" s="34">
         <v>4</v>
       </c>
@@ -4293,10 +4384,10 @@
         <v>12</v>
       </c>
       <c r="M26" s="34" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N26" s="34" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="O26" s="34"/>
       <c r="P26" s="34"/>
@@ -4304,27 +4395,31 @@
     </row>
     <row r="27" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="29" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B27" s="29" t="str">
         <f t="shared" si="2"/>
         <v>One-Eye</v>
       </c>
       <c r="C27" s="29" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E27" s="29" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F27" s="29" t="b">
         <v>0</v>
       </c>
       <c r="G27" s="29"/>
-      <c r="H27" s="29"/>
-      <c r="I27" s="29"/>
+      <c r="H27" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="I27" s="29" t="s">
+        <v>11</v>
+      </c>
       <c r="J27" s="29">
         <v>9</v>
       </c>
@@ -4333,13 +4428,13 @@
         <v>9</v>
       </c>
       <c r="L27" s="29" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M27" s="29" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N27" s="29" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="O27" s="29"/>
       <c r="P27" s="29"/>
@@ -4347,29 +4442,33 @@
     </row>
     <row r="28" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="34" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B28" s="34" t="str">
         <f t="shared" si="2"/>
         <v>Weasel Lackey</v>
       </c>
       <c r="C28" s="34" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D28" s="34" t="s">
+        <v>229</v>
+      </c>
+      <c r="E28" s="34" t="s">
         <v>232</v>
       </c>
-      <c r="E28" s="34" t="s">
-        <v>235</v>
-      </c>
       <c r="F28" s="34" t="b">
         <v>0</v>
       </c>
       <c r="G28" s="34" t="s">
-        <v>239</v>
-      </c>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
+        <v>236</v>
+      </c>
+      <c r="H28" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="I28" s="34" t="s">
+        <v>11</v>
+      </c>
       <c r="J28" s="34">
         <v>2</v>
       </c>
@@ -4381,10 +4480,10 @@
         <v>12</v>
       </c>
       <c r="M28" s="34" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N28" s="34" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="O28" s="34"/>
       <c r="P28" s="34"/>
@@ -4392,29 +4491,33 @@
     </row>
     <row r="29" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="29" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B29" s="29" t="str">
         <f t="shared" si="2"/>
         <v>Left Guard</v>
       </c>
       <c r="C29" s="29" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E29" s="29" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F29" s="29" t="b">
         <v>0</v>
       </c>
       <c r="G29" s="29" t="s">
-        <v>240</v>
-      </c>
-      <c r="H29" s="29"/>
-      <c r="I29" s="29"/>
+        <v>237</v>
+      </c>
+      <c r="H29" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="I29" s="29" t="s">
+        <v>11</v>
+      </c>
       <c r="J29" s="29">
         <v>5</v>
       </c>
@@ -4423,13 +4526,13 @@
         <v>5</v>
       </c>
       <c r="L29" s="29" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M29" s="29" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N29" s="29" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="O29" s="29"/>
       <c r="P29" s="29"/>
@@ -4437,29 +4540,33 @@
     </row>
     <row r="30" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="34" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B30" s="34" t="str">
         <f t="shared" si="2"/>
         <v>Right Guard</v>
       </c>
       <c r="C30" s="34" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D30" s="34" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E30" s="34" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F30" s="34" t="b">
         <v>0</v>
       </c>
       <c r="G30" s="34" t="s">
-        <v>239</v>
-      </c>
-      <c r="H30" s="34"/>
-      <c r="I30" s="34"/>
+        <v>236</v>
+      </c>
+      <c r="H30" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="I30" s="34" t="s">
+        <v>11</v>
+      </c>
       <c r="J30" s="34">
         <v>4</v>
       </c>
@@ -4468,13 +4575,13 @@
         <v>4</v>
       </c>
       <c r="L30" s="34" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M30" s="34" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N30" s="34" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="O30" s="34"/>
       <c r="P30" s="34"/>
@@ -4482,27 +4589,31 @@
     </row>
     <row r="31" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="29" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B31" s="29" t="str">
         <f t="shared" si="2"/>
         <v>Guard Captain</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E31" s="29" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F31" s="29" t="b">
         <v>0</v>
       </c>
       <c r="G31" s="29"/>
-      <c r="H31" s="29"/>
-      <c r="I31" s="29"/>
+      <c r="H31" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="I31" s="29" t="s">
+        <v>11</v>
+      </c>
       <c r="J31" s="29">
         <v>6</v>
       </c>
@@ -4511,13 +4622,13 @@
         <v>6</v>
       </c>
       <c r="L31" s="29" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M31" s="29" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N31" s="29" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="O31" s="29"/>
       <c r="P31" s="29"/>
@@ -4525,29 +4636,33 @@
     </row>
     <row r="32" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="53" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B32" s="34" t="str">
         <f>A32</f>
         <v>Shadow_1</v>
       </c>
       <c r="C32" s="34" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D32" s="34" t="s">
+        <v>229</v>
+      </c>
+      <c r="E32" s="34" t="s">
         <v>232</v>
       </c>
-      <c r="E32" s="34" t="s">
-        <v>235</v>
-      </c>
       <c r="F32" s="34" t="b">
         <v>0</v>
       </c>
       <c r="G32" s="53" t="s">
-        <v>475</v>
-      </c>
-      <c r="H32" s="34"/>
-      <c r="I32" s="34"/>
+        <v>472</v>
+      </c>
+      <c r="H32" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="I32" s="34" t="s">
+        <v>11</v>
+      </c>
       <c r="J32" s="34">
         <v>6</v>
       </c>
@@ -4556,13 +4671,13 @@
         <v>6</v>
       </c>
       <c r="L32" s="34" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M32" s="34" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N32" s="53" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="O32" s="34"/>
       <c r="P32" s="34"/>
@@ -4570,29 +4685,33 @@
     </row>
     <row r="33" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="29" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B33" s="29" t="str">
         <f>A33</f>
         <v>Shadow_2</v>
       </c>
       <c r="C33" s="29" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E33" s="29" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F33" s="29" t="b">
         <v>0</v>
       </c>
       <c r="G33" s="29" t="s">
-        <v>475</v>
-      </c>
-      <c r="H33" s="29"/>
-      <c r="I33" s="29"/>
+        <v>472</v>
+      </c>
+      <c r="H33" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="I33" s="29" t="s">
+        <v>11</v>
+      </c>
       <c r="J33" s="29">
         <v>8</v>
       </c>
@@ -4601,13 +4720,13 @@
         <v>8</v>
       </c>
       <c r="L33" s="29" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M33" s="29" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N33" s="29" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="O33" s="29"/>
       <c r="P33" s="29"/>
@@ -4615,29 +4734,33 @@
     </row>
     <row r="34" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B34" s="34" t="str">
         <f t="shared" si="2"/>
         <v>Shadow_3</v>
       </c>
       <c r="C34" s="34" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D34" s="34" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E34" s="34" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F34" s="34" t="b">
         <v>0</v>
       </c>
       <c r="G34" s="34" t="s">
-        <v>475</v>
-      </c>
-      <c r="H34" s="34"/>
-      <c r="I34" s="34"/>
+        <v>472</v>
+      </c>
+      <c r="H34" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="I34" s="34" t="s">
+        <v>11</v>
+      </c>
       <c r="J34" s="34">
         <v>6</v>
       </c>
@@ -4649,10 +4772,10 @@
         <v>12</v>
       </c>
       <c r="M34" s="34" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N34" s="53" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="O34" s="34"/>
       <c r="P34" s="34"/>
@@ -4660,29 +4783,33 @@
     </row>
     <row r="35" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="29" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B35" s="29" t="str">
         <f t="shared" si="2"/>
         <v>Hand-Mirage</v>
       </c>
       <c r="C35" s="29" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E35" s="29" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F35" s="29" t="b">
         <v>0</v>
       </c>
       <c r="G35" s="29" t="s">
-        <v>241</v>
-      </c>
-      <c r="H35" s="29"/>
-      <c r="I35" s="29"/>
+        <v>238</v>
+      </c>
+      <c r="H35" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="I35" s="29" t="s">
+        <v>11</v>
+      </c>
       <c r="J35" s="29">
         <v>9</v>
       </c>
@@ -4691,13 +4818,13 @@
         <v>9</v>
       </c>
       <c r="L35" s="29" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M35" s="29" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N35" s="29" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="O35" s="29"/>
       <c r="P35" s="29"/>
@@ -4705,27 +4832,31 @@
     </row>
     <row r="36" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="34" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B36" s="34" t="str">
         <f t="shared" si="2"/>
         <v>Cleric</v>
       </c>
       <c r="C36" s="34" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D36" s="34" t="s">
+        <v>230</v>
+      </c>
+      <c r="E36" s="34" t="s">
         <v>233</v>
       </c>
-      <c r="E36" s="34" t="s">
-        <v>236</v>
-      </c>
       <c r="F36" s="34" t="b">
         <v>0</v>
       </c>
       <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
-      <c r="I36" s="34"/>
+      <c r="H36" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="I36" s="34" t="s">
+        <v>11</v>
+      </c>
       <c r="J36" s="34">
         <v>5</v>
       </c>
@@ -4734,13 +4865,13 @@
         <v>5</v>
       </c>
       <c r="L36" s="34" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M36" s="34" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N36" s="53" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="O36" s="34"/>
       <c r="P36" s="34"/>
@@ -4748,27 +4879,31 @@
     </row>
     <row r="37" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="29" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B37" s="29" t="str">
         <f>A37</f>
         <v>Prism Dancer_1</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E37" s="29" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F37" s="29" t="b">
         <v>0</v>
       </c>
       <c r="G37" s="29"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="29"/>
+      <c r="H37" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="I37" s="29" t="s">
+        <v>11</v>
+      </c>
       <c r="J37" s="29">
         <v>4</v>
       </c>
@@ -4777,13 +4912,13 @@
         <v>4</v>
       </c>
       <c r="L37" s="29" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M37" s="29" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N37" s="29" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="O37" s="29"/>
       <c r="P37" s="29"/>
@@ -4791,27 +4926,31 @@
     </row>
     <row r="38" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="37" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B38" s="37" t="str">
         <f t="shared" ref="B38" si="3">A38</f>
         <v>Prism Dancer_2</v>
       </c>
       <c r="C38" s="37" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F38" s="37" t="b">
         <v>0</v>
       </c>
       <c r="G38" s="37"/>
-      <c r="H38" s="37"/>
-      <c r="I38" s="37"/>
+      <c r="H38" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="I38" s="37" t="s">
+        <v>11</v>
+      </c>
       <c r="J38" s="37">
         <v>4</v>
       </c>
@@ -4820,13 +4959,13 @@
         <v>4</v>
       </c>
       <c r="L38" s="37" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M38" s="37" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N38" s="37" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="O38" s="37"/>
       <c r="P38" s="37"/>
@@ -4834,26 +4973,32 @@
     </row>
     <row r="39" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="38" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B39" s="11" t="str">
         <f t="shared" si="2"/>
         <v>Bog Monkey</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F39" s="11" t="b">
         <v>0</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>240</v>
+        <v>237</v>
+      </c>
+      <c r="H39" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="I39" s="11" t="s">
+        <v>11</v>
       </c>
       <c r="J39" s="11">
         <v>5</v>
@@ -4866,35 +5011,39 @@
         <v>12</v>
       </c>
       <c r="M39" s="11" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N39" s="29" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="39" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B40" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Bog Sage</v>
       </c>
       <c r="C40" s="39" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D40" s="39" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E40" s="39" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F40" s="39" t="b">
         <v>0</v>
       </c>
       <c r="G40" s="39"/>
-      <c r="H40" s="39"/>
-      <c r="I40" s="39"/>
+      <c r="H40" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="I40" s="39" t="s">
+        <v>11</v>
+      </c>
       <c r="J40" s="39">
         <v>8</v>
       </c>
@@ -4903,13 +5052,13 @@
         <v>8</v>
       </c>
       <c r="L40" s="39" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M40" s="39" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N40" s="39" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="O40" s="39"/>
       <c r="P40" s="39"/>
@@ -4917,29 +5066,33 @@
     </row>
     <row r="41" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="38" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B41" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Rubber Logistics Soldier</v>
       </c>
       <c r="C41" s="38" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D41" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="E41" s="38" t="s">
         <v>232</v>
       </c>
-      <c r="E41" s="38" t="s">
-        <v>235</v>
-      </c>
       <c r="F41" s="38" t="b">
         <v>0</v>
       </c>
       <c r="G41" s="38" t="s">
-        <v>242</v>
-      </c>
-      <c r="H41" s="38"/>
-      <c r="I41" s="38"/>
+        <v>239</v>
+      </c>
+      <c r="H41" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="I41" s="38" t="s">
+        <v>11</v>
+      </c>
       <c r="J41" s="38">
         <v>2</v>
       </c>
@@ -4948,13 +5101,13 @@
         <v>2</v>
       </c>
       <c r="L41" s="38" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M41" s="38" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N41" s="38" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="O41" s="38"/>
       <c r="P41" s="38"/>
@@ -4962,29 +5115,33 @@
     </row>
     <row r="42" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="39" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B42" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Tiger</v>
       </c>
       <c r="C42" s="39" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D42" s="39" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E42" s="39" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F42" s="39" t="b">
         <v>0</v>
       </c>
       <c r="G42" s="39" t="s">
-        <v>242</v>
-      </c>
-      <c r="H42" s="39"/>
-      <c r="I42" s="39"/>
+        <v>239</v>
+      </c>
+      <c r="H42" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="I42" s="39" t="s">
+        <v>11</v>
+      </c>
       <c r="J42" s="39">
         <v>8</v>
       </c>
@@ -4993,13 +5150,13 @@
         <v>8</v>
       </c>
       <c r="L42" s="39" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M42" s="39" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N42" s="39" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="O42" s="39"/>
       <c r="P42" s="39"/>
@@ -5007,29 +5164,33 @@
     </row>
     <row r="43" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="38" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B43" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Ghost Warrior</v>
       </c>
       <c r="C43" s="38" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E43" s="38" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F43" s="38" t="b">
         <v>0</v>
       </c>
       <c r="G43" s="38" t="s">
-        <v>243</v>
-      </c>
-      <c r="H43" s="38"/>
-      <c r="I43" s="38"/>
+        <v>240</v>
+      </c>
+      <c r="H43" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="I43" s="38" t="s">
+        <v>11</v>
+      </c>
       <c r="J43" s="38">
         <v>2</v>
       </c>
@@ -5038,13 +5199,13 @@
         <v>2</v>
       </c>
       <c r="L43" s="38" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="M43" s="38" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N43" s="38" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="O43" s="38"/>
       <c r="P43" s="38"/>
@@ -5052,31 +5213,33 @@
     </row>
     <row r="44" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="39" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B44" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Gustav Railway Cannon</v>
       </c>
       <c r="C44" s="39" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D44" s="39" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E44" s="39" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F44" s="39" t="b">
         <v>0</v>
       </c>
       <c r="G44" s="39" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="H44" s="39" t="s">
-        <v>477</v>
-      </c>
-      <c r="I44" s="39"/>
+        <v>474</v>
+      </c>
+      <c r="I44" s="39" t="s">
+        <v>11</v>
+      </c>
       <c r="J44" s="39">
         <v>12</v>
       </c>
@@ -5085,13 +5248,13 @@
         <v>12</v>
       </c>
       <c r="L44" s="39" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M44" s="39" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N44" s="39" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="O44" s="39"/>
       <c r="P44" s="39"/>
@@ -5099,31 +5262,33 @@
     </row>
     <row r="45" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="38" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B45" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Rubber Artillery</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E45" s="38" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F45" s="38" t="b">
         <v>0</v>
       </c>
       <c r="G45" s="38" t="s">
-        <v>244</v>
-      </c>
-      <c r="H45" s="38" t="s">
-        <v>239</v>
-      </c>
-      <c r="I45" s="38"/>
+        <v>241</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="I45" s="38" t="s">
+        <v>11</v>
+      </c>
       <c r="J45" s="38">
         <v>3</v>
       </c>
@@ -5132,13 +5297,13 @@
         <v>3</v>
       </c>
       <c r="L45" s="38" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="M45" s="38" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N45" s="38" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="O45" s="38"/>
       <c r="P45" s="38"/>
@@ -5146,29 +5311,33 @@
     </row>
     <row r="46" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="39" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B46" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Voidwarden of Pale</v>
       </c>
       <c r="C46" s="39" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D46" s="39" t="s">
+        <v>230</v>
+      </c>
+      <c r="E46" s="39" t="s">
         <v>233</v>
       </c>
-      <c r="E46" s="39" t="s">
+      <c r="F46" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="G46" s="39" t="s">
         <v>236</v>
       </c>
-      <c r="F46" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="G46" s="39" t="s">
-        <v>239</v>
-      </c>
-      <c r="H46" s="39"/>
-      <c r="I46" s="39"/>
+      <c r="H46" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="I46" s="39" t="s">
+        <v>11</v>
+      </c>
       <c r="J46" s="39">
         <v>8</v>
       </c>
@@ -5177,13 +5346,13 @@
         <v>8</v>
       </c>
       <c r="L46" s="39" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M46" s="39" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N46" s="39" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="O46" s="39"/>
       <c r="P46" s="39"/>
@@ -5191,29 +5360,33 @@
     </row>
     <row r="47" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="38" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B47" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Voidwarden of Abyss</v>
       </c>
       <c r="C47" s="38" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D47" s="38" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E47" s="38" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F47" s="38" t="b">
         <v>0</v>
       </c>
       <c r="G47" s="38" t="s">
-        <v>240</v>
-      </c>
-      <c r="H47" s="38"/>
-      <c r="I47" s="38"/>
+        <v>237</v>
+      </c>
+      <c r="H47" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="I47" s="38" t="s">
+        <v>11</v>
+      </c>
       <c r="J47" s="38">
         <v>8</v>
       </c>
@@ -5222,13 +5395,13 @@
         <v>8</v>
       </c>
       <c r="L47" s="38" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M47" s="38" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N47" s="38" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="O47" s="38"/>
       <c r="P47" s="38"/>
@@ -5236,29 +5409,33 @@
     </row>
     <row r="48" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="39" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B48" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Cursed Tree</v>
       </c>
       <c r="C48" s="39" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D48" s="39" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E48" s="39" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F48" s="39" t="b">
         <v>0</v>
       </c>
       <c r="G48" s="39" t="s">
-        <v>239</v>
-      </c>
-      <c r="H48" s="39"/>
-      <c r="I48" s="39"/>
+        <v>236</v>
+      </c>
+      <c r="H48" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="I48" s="39" t="s">
+        <v>11</v>
+      </c>
       <c r="J48" s="39">
         <v>14</v>
       </c>
@@ -5267,13 +5444,13 @@
         <v>14</v>
       </c>
       <c r="L48" s="39" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M48" s="39" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N48" s="39" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="O48" s="39"/>
       <c r="P48" s="39"/>
@@ -5281,29 +5458,33 @@
     </row>
     <row r="49" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="38" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B49" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Porcupine</v>
       </c>
       <c r="C49" s="38" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D49" s="38" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E49" s="38" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F49" s="38" t="b">
         <v>0</v>
       </c>
       <c r="G49" s="38" t="s">
-        <v>239</v>
-      </c>
-      <c r="H49" s="38"/>
-      <c r="I49" s="38"/>
+        <v>236</v>
+      </c>
+      <c r="H49" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="I49" s="38" t="s">
+        <v>11</v>
+      </c>
       <c r="J49" s="38">
         <v>5</v>
       </c>
@@ -5312,13 +5493,13 @@
         <v>5</v>
       </c>
       <c r="L49" s="38" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M49" s="38" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N49" s="38" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="O49" s="38"/>
       <c r="P49" s="38"/>
@@ -5326,29 +5507,33 @@
     </row>
     <row r="50" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="39" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B50" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Tree Spirit</v>
       </c>
       <c r="C50" s="39" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D50" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="E50" s="39" t="s">
         <v>232</v>
       </c>
-      <c r="E50" s="39" t="s">
-        <v>235</v>
-      </c>
       <c r="F50" s="39" t="b">
         <v>0</v>
       </c>
       <c r="G50" s="39" t="s">
-        <v>240</v>
-      </c>
-      <c r="H50" s="39"/>
-      <c r="I50" s="39"/>
+        <v>237</v>
+      </c>
+      <c r="H50" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="I50" s="39" t="s">
+        <v>11</v>
+      </c>
       <c r="J50" s="39">
         <v>3</v>
       </c>
@@ -5357,13 +5542,13 @@
         <v>3</v>
       </c>
       <c r="L50" s="39" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M50" s="39" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N50" s="39" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="O50" s="39"/>
       <c r="P50" s="39"/>
@@ -5371,29 +5556,31 @@
     </row>
     <row r="51" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="38" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B51" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Coyote</v>
       </c>
       <c r="C51" s="38" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D51" s="43" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E51" s="38" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F51" s="38" t="b">
         <v>0</v>
       </c>
       <c r="G51" s="38"/>
       <c r="H51" s="38" t="s">
-        <v>240</v>
-      </c>
-      <c r="I51" s="38"/>
+        <v>237</v>
+      </c>
+      <c r="I51" s="38" t="s">
+        <v>11</v>
+      </c>
       <c r="J51" s="38">
         <v>2</v>
       </c>
@@ -5402,13 +5589,13 @@
         <v>2</v>
       </c>
       <c r="L51" s="38" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M51" s="38" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N51" s="38" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="O51" s="38"/>
       <c r="P51" s="38"/>
@@ -5416,25 +5603,29 @@
     </row>
     <row r="52" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="39" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B52" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Brave·Left Hand</v>
       </c>
       <c r="C52" s="39" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D52" s="45"/>
       <c r="E52" s="39" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F52" s="39" t="b">
         <v>0</v>
       </c>
       <c r="G52" s="39"/>
-      <c r="H52" s="39"/>
-      <c r="I52" s="39"/>
+      <c r="H52" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="I52" s="39" t="s">
+        <v>11</v>
+      </c>
       <c r="J52" s="39">
         <v>9</v>
       </c>
@@ -5443,13 +5634,13 @@
         <v>9</v>
       </c>
       <c r="L52" s="39" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M52" s="39" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N52" s="39" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="O52" s="39"/>
       <c r="P52" s="39"/>
@@ -5457,25 +5648,29 @@
     </row>
     <row r="53" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="38" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B53" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Brave·Right Hand</v>
       </c>
       <c r="C53" s="42" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D53" s="46"/>
       <c r="E53" s="38" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F53" s="38" t="b">
         <v>0</v>
       </c>
       <c r="G53" s="38"/>
-      <c r="H53" s="38"/>
-      <c r="I53" s="44"/>
+      <c r="H53" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="I53" s="44" t="s">
+        <v>11</v>
+      </c>
       <c r="J53" s="38">
         <v>9</v>
       </c>
@@ -5484,13 +5679,13 @@
         <v>9</v>
       </c>
       <c r="L53" s="38" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M53" s="38" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N53" s="38" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="O53" s="38"/>
       <c r="P53" s="38"/>
@@ -5498,29 +5693,31 @@
     </row>
     <row r="54" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="39" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B54" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Fear</v>
       </c>
       <c r="C54" s="39" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D54" s="39" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E54" s="39" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F54" s="39" t="b">
         <v>0</v>
       </c>
       <c r="G54" s="39"/>
       <c r="H54" s="39" t="s">
-        <v>246</v>
-      </c>
-      <c r="I54" s="39"/>
+        <v>243</v>
+      </c>
+      <c r="I54" s="39" t="s">
+        <v>11</v>
+      </c>
       <c r="J54" s="39">
         <v>6</v>
       </c>
@@ -5529,13 +5726,13 @@
         <v>6</v>
       </c>
       <c r="L54" s="39" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M54" s="39" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N54" s="39" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="O54" s="39"/>
       <c r="P54" s="39"/>
@@ -5543,27 +5740,31 @@
     </row>
     <row r="55" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="38" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B55" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Unbroken Will</v>
       </c>
       <c r="C55" s="38" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D55" s="38" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E55" s="38" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F55" s="38" t="b">
         <v>0</v>
       </c>
       <c r="G55" s="38"/>
-      <c r="H55" s="38"/>
-      <c r="I55" s="38"/>
+      <c r="H55" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="I55" s="38" t="s">
+        <v>11</v>
+      </c>
       <c r="J55" s="38">
         <v>4</v>
       </c>
@@ -5572,13 +5773,13 @@
         <v>4</v>
       </c>
       <c r="L55" s="38" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M55" s="38" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N55" s="38" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="O55" s="38"/>
       <c r="P55" s="38"/>
@@ -5586,29 +5787,33 @@
     </row>
     <row r="56" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="39" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B56" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Brave of Old</v>
       </c>
       <c r="C56" s="39" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D56" s="39" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E56" s="39" t="s">
+        <v>233</v>
+      </c>
+      <c r="F56" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="G56" s="39" t="s">
         <v>236</v>
       </c>
-      <c r="F56" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="G56" s="39" t="s">
-        <v>239</v>
-      </c>
-      <c r="H56" s="39"/>
-      <c r="I56" s="39"/>
+      <c r="H56" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="I56" s="39" t="s">
+        <v>11</v>
+      </c>
       <c r="J56" s="39">
         <v>8</v>
       </c>
@@ -5617,13 +5822,13 @@
         <v>8</v>
       </c>
       <c r="L56" s="39" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="M56" s="39" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N56" s="39" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="O56" s="39"/>
       <c r="P56" s="39"/>
@@ -5631,29 +5836,33 @@
     </row>
     <row r="57" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="38" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B57" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Ancestral Brave</v>
       </c>
       <c r="C57" s="38" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D57" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="E57" s="38" t="s">
         <v>233</v>
       </c>
-      <c r="E57" s="38" t="s">
+      <c r="F57" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="G57" s="38" t="s">
         <v>236</v>
       </c>
-      <c r="F57" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="G57" s="38" t="s">
-        <v>239</v>
-      </c>
-      <c r="H57" s="38"/>
-      <c r="I57" s="38"/>
+      <c r="H57" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="I57" s="38" t="s">
+        <v>11</v>
+      </c>
       <c r="J57" s="38">
         <v>15</v>
       </c>
@@ -5662,13 +5871,13 @@
         <v>15</v>
       </c>
       <c r="L57" s="38" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M57" s="38" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N57" s="38" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="O57" s="38"/>
       <c r="P57" s="38"/>
@@ -5676,29 +5885,33 @@
     </row>
     <row r="58" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="39" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B58" s="39" t="str">
         <f t="shared" si="2"/>
         <v>Oathblade</v>
       </c>
       <c r="C58" s="39" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D58" s="39" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E58" s="39" t="s">
+        <v>233</v>
+      </c>
+      <c r="F58" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="G58" s="39" t="s">
         <v>236</v>
       </c>
-      <c r="F58" s="39" t="b">
-        <v>0</v>
-      </c>
-      <c r="G58" s="39" t="s">
-        <v>239</v>
-      </c>
-      <c r="H58" s="39"/>
-      <c r="I58" s="39"/>
+      <c r="H58" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="I58" s="39" t="s">
+        <v>11</v>
+      </c>
       <c r="J58" s="39">
         <v>8</v>
       </c>
@@ -5707,13 +5920,13 @@
         <v>8</v>
       </c>
       <c r="L58" s="39" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M58" s="39" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N58" s="39" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="O58" s="39"/>
       <c r="P58" s="39"/>
@@ -5721,20 +5934,20 @@
     </row>
     <row r="59" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="38" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B59" s="11" t="str">
         <f t="shared" si="2"/>
         <v>Void Lock</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F59" s="11" t="b">
         <v>0</v>
@@ -5751,28 +5964,28 @@
         <v>12</v>
       </c>
       <c r="M59" s="11" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N59" s="29" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="60" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="41" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B60" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Void Cage</v>
       </c>
       <c r="C60" s="41" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D60" s="41" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E60" s="41" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F60" s="41" t="b">
         <v>0</v>
@@ -5788,13 +6001,13 @@
         <v>8</v>
       </c>
       <c r="L60" s="41" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M60" s="41" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N60" s="41" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="O60" s="41"/>
       <c r="P60" s="41"/>
@@ -5802,26 +6015,26 @@
     </row>
     <row r="61" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="38" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B61" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Rat</v>
       </c>
       <c r="C61" s="38" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D61" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="E61" s="38" t="s">
         <v>232</v>
       </c>
-      <c r="E61" s="38" t="s">
-        <v>235</v>
-      </c>
       <c r="F61" s="38" t="b">
         <v>0</v>
       </c>
       <c r="G61" s="38" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H61" s="38"/>
       <c r="I61" s="38"/>
@@ -5833,13 +6046,13 @@
         <v>3</v>
       </c>
       <c r="L61" s="38" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M61" s="38" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N61" s="38" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="O61" s="38"/>
       <c r="P61" s="38"/>
@@ -5847,26 +6060,26 @@
     </row>
     <row r="62" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="41" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B62" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Rat King</v>
       </c>
       <c r="C62" s="41" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D62" s="41" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E62" s="41" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F62" s="41" t="b">
         <v>0</v>
       </c>
       <c r="G62" s="41" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="H62" s="41"/>
       <c r="I62" s="41"/>
@@ -5878,13 +6091,13 @@
         <v>10</v>
       </c>
       <c r="L62" s="41" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M62" s="41" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N62" s="41" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="O62" s="41"/>
       <c r="P62" s="41"/>
@@ -5892,20 +6105,20 @@
     </row>
     <row r="63" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="38" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B63" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Frog</v>
       </c>
       <c r="C63" s="38" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D63" s="38" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E63" s="38" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F63" s="38" t="b">
         <v>0</v>
@@ -5921,13 +6134,13 @@
         <v>7</v>
       </c>
       <c r="L63" s="38" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M63" s="38" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N63" s="38" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="O63" s="38"/>
       <c r="P63" s="38"/>
@@ -5935,20 +6148,20 @@
     </row>
     <row r="64" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="41" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B64" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Horse</v>
       </c>
       <c r="C64" s="41" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D64" s="41" t="s">
+        <v>230</v>
+      </c>
+      <c r="E64" s="41" t="s">
         <v>233</v>
-      </c>
-      <c r="E64" s="41" t="s">
-        <v>236</v>
       </c>
       <c r="F64" s="41" t="b">
         <v>0</v>
@@ -5964,13 +6177,13 @@
         <v>9</v>
       </c>
       <c r="L64" s="41" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M64" s="41" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N64" s="41" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="O64" s="41"/>
       <c r="P64" s="41"/>
@@ -5978,20 +6191,20 @@
     </row>
     <row r="65" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="38" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B65" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Fruit Fly</v>
       </c>
       <c r="C65" s="38" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D65" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="E65" s="38" t="s">
         <v>232</v>
-      </c>
-      <c r="E65" s="38" t="s">
-        <v>235</v>
       </c>
       <c r="F65" s="38" t="b">
         <v>0</v>
@@ -6007,13 +6220,13 @@
         <v>2</v>
       </c>
       <c r="L65" s="38" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M65" s="38" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N65" s="38" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="O65" s="38"/>
       <c r="P65" s="38"/>
@@ -6021,20 +6234,20 @@
     </row>
     <row r="66" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="41" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B66" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Unsoiled Seed</v>
       </c>
       <c r="C66" s="41" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D66" s="41" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E66" s="41" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F66" s="41" t="b">
         <v>0</v>
@@ -6050,13 +6263,13 @@
         <v>5</v>
       </c>
       <c r="L66" s="41" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M66" s="41" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N66" s="41" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="O66" s="41"/>
       <c r="P66" s="41"/>
@@ -6064,20 +6277,20 @@
     </row>
     <row r="67" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="38" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B67" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Evergreen</v>
       </c>
       <c r="C67" s="38" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D67" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="E67" s="38" t="s">
         <v>233</v>
-      </c>
-      <c r="E67" s="38" t="s">
-        <v>236</v>
       </c>
       <c r="F67" s="38" t="b">
         <v>0</v>
@@ -6093,13 +6306,13 @@
         <v>9</v>
       </c>
       <c r="L67" s="38" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M67" s="38" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N67" s="38" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="O67" s="38"/>
       <c r="P67" s="38"/>
@@ -6107,20 +6320,20 @@
     </row>
     <row r="68" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="41" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B68" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Unhatch Being</v>
       </c>
       <c r="C68" s="41" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D68" s="41" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E68" s="41" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F68" s="41" t="b">
         <v>0</v>
@@ -6136,13 +6349,13 @@
         <v>6</v>
       </c>
       <c r="L68" s="41" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M68" s="41" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N68" s="41" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="O68" s="41"/>
       <c r="P68" s="41"/>
@@ -6150,20 +6363,20 @@
     </row>
     <row r="69" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="38" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B69" s="38" t="str">
         <f t="shared" si="2"/>
         <v>White Dove</v>
       </c>
       <c r="C69" s="38" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D69" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="E69" s="38" t="s">
         <v>233</v>
-      </c>
-      <c r="E69" s="38" t="s">
-        <v>236</v>
       </c>
       <c r="F69" s="38" t="b">
         <v>0</v>
@@ -6179,13 +6392,13 @@
         <v>7</v>
       </c>
       <c r="L69" s="38" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M69" s="38" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N69" s="38" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="O69" s="38"/>
       <c r="P69" s="38"/>
@@ -6193,20 +6406,20 @@
     </row>
     <row r="70" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="41" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B70" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Unquenched Flame</v>
       </c>
       <c r="C70" s="41" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D70" s="41" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E70" s="41" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F70" s="41" t="b">
         <v>0</v>
@@ -6222,13 +6435,13 @@
         <v>9</v>
       </c>
       <c r="L70" s="41" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M70" s="41" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N70" s="41" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="O70" s="41"/>
       <c r="P70" s="41"/>
@@ -6236,26 +6449,26 @@
     </row>
     <row r="71" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="38" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B71" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Phoenix</v>
       </c>
       <c r="C71" s="38" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D71" s="38" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E71" s="38" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F71" s="38" t="b">
         <v>0</v>
       </c>
       <c r="G71" s="38" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="H71" s="38"/>
       <c r="I71" s="38"/>
@@ -6267,13 +6480,13 @@
         <v>13</v>
       </c>
       <c r="L71" s="38" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M71" s="38" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N71" s="38" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="O71" s="38"/>
       <c r="P71" s="38"/>
@@ -6281,20 +6494,20 @@
     </row>
     <row r="72" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="41" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B72" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Child</v>
       </c>
       <c r="C72" s="41" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D72" s="41" t="s">
+        <v>230</v>
+      </c>
+      <c r="E72" s="41" t="s">
         <v>233</v>
-      </c>
-      <c r="E72" s="41" t="s">
-        <v>236</v>
       </c>
       <c r="F72" s="41" t="b">
         <v>0</v>
@@ -6310,13 +6523,13 @@
         <v>10</v>
       </c>
       <c r="L72" s="41" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M72" s="41" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N72" s="41" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="O72" s="41"/>
       <c r="P72" s="41"/>
@@ -6324,26 +6537,26 @@
     </row>
     <row r="73" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="38" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B73" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Dust-Sealed Heart</v>
       </c>
       <c r="C73" s="38" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D73" s="38" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E73" s="38" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F73" s="38" t="b">
         <v>0</v>
       </c>
       <c r="G73" s="38" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="H73" s="38"/>
       <c r="I73" s="38"/>
@@ -6355,13 +6568,13 @@
         <v>7</v>
       </c>
       <c r="L73" s="38" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M73" s="38" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N73" s="38" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="O73" s="38"/>
       <c r="P73" s="38"/>
@@ -6369,29 +6582,29 @@
     </row>
     <row r="74" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="41" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B74" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Ronin</v>
       </c>
       <c r="C74" s="41" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D74" s="41" t="s">
+        <v>229</v>
+      </c>
+      <c r="E74" s="41" t="s">
         <v>232</v>
       </c>
-      <c r="E74" s="41" t="s">
-        <v>235</v>
-      </c>
       <c r="F74" s="41" t="b">
         <v>0</v>
       </c>
       <c r="G74" s="41" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H74" s="41" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="I74" s="41"/>
       <c r="J74" s="41">
@@ -6402,13 +6615,13 @@
         <v>4</v>
       </c>
       <c r="L74" s="41" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M74" s="41" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N74" s="41" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="O74" s="41"/>
       <c r="P74" s="41"/>
@@ -6416,29 +6629,29 @@
     </row>
     <row r="75" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="38" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B75" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Mortis</v>
       </c>
       <c r="C75" s="38" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D75" s="38" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E75" s="38" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F75" s="38" t="b">
         <v>0</v>
       </c>
       <c r="G75" s="38" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H75" s="38" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="I75" s="38"/>
       <c r="J75" s="38">
@@ -6449,13 +6662,13 @@
         <v>2</v>
       </c>
       <c r="L75" s="38" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M75" s="38" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N75" s="38" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="O75" s="38"/>
       <c r="P75" s="38"/>
@@ -6463,26 +6676,26 @@
     </row>
     <row r="76" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="41" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B76" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Slasher</v>
       </c>
       <c r="C76" s="41" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D76" s="41" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E76" s="41" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F76" s="41" t="b">
         <v>0</v>
       </c>
       <c r="G76" s="41" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H76" s="41"/>
       <c r="I76" s="41"/>
@@ -6494,13 +6707,13 @@
         <v>13</v>
       </c>
       <c r="L76" s="41" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="M76" s="41" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N76" s="41" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="O76" s="41"/>
       <c r="P76" s="41"/>
@@ -6508,20 +6721,20 @@
     </row>
     <row r="77" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="38" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B77" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Tainted Gipsy</v>
       </c>
       <c r="C77" s="38" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D77" s="38" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E77" s="38" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F77" s="38" t="b">
         <v>0</v>
@@ -6537,13 +6750,13 @@
         <v>20</v>
       </c>
       <c r="L77" s="38" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M77" s="38" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N77" s="38" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="O77" s="38"/>
       <c r="P77" s="38"/>
@@ -6551,26 +6764,26 @@
     </row>
     <row r="78" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="41" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B78" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Hall-warden</v>
       </c>
       <c r="C78" s="41" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D78" s="41" t="s">
+        <v>230</v>
+      </c>
+      <c r="E78" s="41" t="s">
         <v>233</v>
       </c>
-      <c r="E78" s="41" t="s">
-        <v>236</v>
-      </c>
       <c r="F78" s="41" t="b">
         <v>0</v>
       </c>
       <c r="G78" s="41" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="H78" s="41"/>
       <c r="I78" s="41"/>
@@ -6582,13 +6795,13 @@
         <v>10</v>
       </c>
       <c r="L78" s="41" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M78" s="41" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N78" s="41" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="O78" s="41"/>
       <c r="P78" s="41"/>
@@ -6596,20 +6809,20 @@
     </row>
     <row r="79" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="38" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B79" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Athena</v>
       </c>
       <c r="C79" s="38" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D79" s="38" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E79" s="38" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F79" s="38" t="b">
         <v>0</v>
@@ -6625,13 +6838,13 @@
         <v>12</v>
       </c>
       <c r="L79" s="38" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M79" s="38" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N79" s="38" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="O79" s="38"/>
       <c r="P79" s="38"/>
@@ -6639,20 +6852,20 @@
     </row>
     <row r="80" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="41" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B80" s="41" t="str">
         <f t="shared" si="2"/>
         <v>Skyburner</v>
       </c>
       <c r="C80" s="41" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D80" s="41" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E80" s="41" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F80" s="41" t="b">
         <v>0</v>
@@ -6668,13 +6881,13 @@
         <v>15</v>
       </c>
       <c r="L80" s="41" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M80" s="41" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N80" s="41" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="O80" s="41"/>
       <c r="P80" s="41"/>
@@ -6682,20 +6895,20 @@
     </row>
     <row r="81" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="38" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B81" s="38" t="str">
         <f t="shared" si="2"/>
         <v>Hand of Corruption</v>
       </c>
       <c r="C81" s="38" t="s">
+        <v>224</v>
+      </c>
+      <c r="D81" s="38" t="s">
         <v>227</v>
       </c>
-      <c r="D81" s="38" t="s">
-        <v>230</v>
-      </c>
       <c r="E81" s="38" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F81" s="38" t="b">
         <v>0</v>
@@ -6711,13 +6924,13 @@
         <v>28</v>
       </c>
       <c r="L81" s="38" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="M81" s="38" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N81" s="38" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="O81" s="38"/>
       <c r="P81" s="38"/>
@@ -6725,20 +6938,20 @@
     </row>
     <row r="82" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="41" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B82" s="41" t="str">
         <f>A82</f>
         <v>Counter-Blade</v>
       </c>
       <c r="C82" s="41" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D82" s="41" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E82" s="41" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F82" s="55" t="b">
         <v>1</v>
@@ -6756,13 +6969,13 @@
         <v>12</v>
       </c>
       <c r="L82" s="41" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="M82" s="41" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="N82" s="41" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="O82" s="41"/>
       <c r="P82" s="41"/>
@@ -6958,7 +7171,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6980,7 +7193,7 @@
     <col min="11" max="11" width="20.25" style="16" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.58203125" style="16" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="23.75" style="16" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.58203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.83203125" style="16" customWidth="1"/>
     <col min="15" max="15" width="15" style="16" bestFit="1" customWidth="1"/>
     <col min="16" max="16384" width="8.9140625" style="16"/>
   </cols>
@@ -6993,7 +7206,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>27</v>
@@ -7014,7 +7227,7 @@
         <v>30</v>
       </c>
       <c r="J1" s="56" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>31</v>
@@ -7026,42 +7239,42 @@
         <v>33</v>
       </c>
       <c r="N1" s="22" t="s">
-        <v>34</v>
+        <v>489</v>
       </c>
       <c r="O1" s="22" t="s">
-        <v>35</v>
+        <v>488</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C2" s="26">
         <v>1</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F2" s="26" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="G2" s="26" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I2" s="26" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="J2" s="26" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="K2" s="6">
         <v>0</v>
@@ -7080,34 +7293,34 @@
     </row>
     <row r="3" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C3" s="27">
         <v>1</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F3" s="51" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I3" s="27" t="s">
+        <v>440</v>
+      </c>
+      <c r="J3" s="27" t="s">
         <v>443</v>
-      </c>
-      <c r="J3" s="27" t="s">
-        <v>446</v>
       </c>
       <c r="K3" s="16">
         <v>0</v>
@@ -7129,34 +7342,34 @@
     </row>
     <row r="4" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C4" s="26">
         <v>1</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I4" s="26" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="K4" s="6">
         <v>1</v>
@@ -7178,34 +7391,34 @@
     </row>
     <row r="5" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C5" s="27">
         <v>1</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F5" s="51" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="J5" s="16" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="K5" s="16">
         <v>1</v>
@@ -7227,34 +7440,34 @@
     </row>
     <row r="6" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="25" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C6" s="26">
         <v>1</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>11</v>
       </c>
       <c r="J6" s="26" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="K6" s="6">
         <v>1</v>
@@ -7263,7 +7476,7 @@
         <v>4</v>
       </c>
       <c r="M6" s="25" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="N6" s="6" t="str">
         <f t="shared" si="1"/>
@@ -7276,34 +7489,34 @@
     </row>
     <row r="7" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C7" s="27">
         <v>2</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F7" s="51" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="J7" s="27" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="K7" s="16">
         <v>1</v>
@@ -7325,34 +7538,34 @@
     </row>
     <row r="8" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="52" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B8" s="52" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C8" s="52">
         <v>2</v>
       </c>
       <c r="D8" s="52" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E8" s="52" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F8" s="52" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G8" s="52" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H8" s="52" t="s">
+        <v>442</v>
+      </c>
+      <c r="I8" s="52" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="52" t="s">
         <v>445</v>
-      </c>
-      <c r="I8" s="52" t="s">
-        <v>45</v>
-      </c>
-      <c r="J8" s="52" t="s">
-        <v>448</v>
       </c>
       <c r="K8" s="62">
         <v>1</v>
@@ -7361,7 +7574,7 @@
         <v>5</v>
       </c>
       <c r="M8" s="52" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="N8" s="52" t="str">
         <f t="shared" si="1"/>
@@ -7374,34 +7587,34 @@
     </row>
     <row r="9" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C9" s="15">
         <v>2</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I9" s="57" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="J9" s="57" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="K9" s="27">
         <v>2</v>
@@ -7423,34 +7636,34 @@
     </row>
     <row r="10" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="52" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B10" s="52" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C10" s="52">
         <v>2</v>
       </c>
       <c r="D10" s="52" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E10" s="52" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F10" s="52" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="G10" s="67" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="H10" s="52" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I10" s="52" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="J10" s="52" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="K10" s="62">
         <v>2</v>
@@ -7472,34 +7685,34 @@
     </row>
     <row r="11" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C11" s="15">
         <v>2</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F11" s="15" t="s">
+        <v>314</v>
+      </c>
+      <c r="G11" s="57" t="s">
         <v>317</v>
       </c>
-      <c r="G11" s="57" t="s">
-        <v>320</v>
-      </c>
       <c r="H11" s="15" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I11" s="57" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="K11" s="27">
         <v>3</v>
@@ -7521,34 +7734,34 @@
     </row>
     <row r="12" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="52" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B12" s="52" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C12" s="52">
         <v>2</v>
       </c>
       <c r="D12" s="52" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="E12" s="52" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F12" s="52" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="G12" s="52" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H12" s="52" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I12" s="52" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="J12" s="52" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="K12" s="62">
         <v>3</v>
@@ -7570,34 +7783,34 @@
     </row>
     <row r="13" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C13" s="27">
         <v>3</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G13" s="51" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I13" s="27" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="J13" s="27" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="K13" s="16">
         <v>3</v>
@@ -7619,34 +7832,34 @@
     </row>
     <row r="14" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="33" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C14" s="33">
         <v>3</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H14" s="33" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I14" s="33" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="J14" s="33" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="K14" s="33">
         <v>4</v>
@@ -7668,34 +7881,34 @@
     </row>
     <row r="15" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C15" s="27">
         <v>3</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I15" s="27" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="K15" s="16">
         <v>4</v>
@@ -7717,34 +7930,34 @@
     </row>
     <row r="16" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="33" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C16" s="33">
         <v>3</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="F16" s="33" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="G16" s="33" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H16" s="33" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I16" s="33" t="s">
         <v>11</v>
       </c>
       <c r="J16" s="33" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="K16" s="33">
         <v>5</v>
@@ -7766,34 +7979,34 @@
     </row>
     <row r="17" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C17" s="27">
         <v>3</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I17" s="27" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="J17" s="27" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="K17" s="16">
         <v>5</v>
@@ -7815,34 +8028,34 @@
     </row>
     <row r="18" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="33" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C18" s="33">
         <v>3</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F18" s="33" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G18" s="33" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H18" s="33" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I18" s="33" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="J18" s="33" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="K18" s="33">
         <v>5</v>
@@ -7864,34 +8077,34 @@
     </row>
     <row r="19" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C19" s="27">
         <v>3</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="F19" s="51" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I19" s="27" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="J19" s="27" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="K19" s="16">
         <v>6</v>
@@ -7913,34 +8126,34 @@
     </row>
     <row r="20" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="39" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C20" s="39">
         <v>4</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E20" s="39" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="F20" s="39" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H20" s="39" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I20" s="39" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="J20" s="39" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="K20" s="39">
         <v>6</v>
@@ -7962,34 +8175,34 @@
     </row>
     <row r="21" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C21" s="27">
         <v>4</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F21" s="51" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I21" s="27" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="J21" s="16" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="K21" s="16">
         <v>6</v>
@@ -8011,34 +8224,34 @@
     </row>
     <row r="22" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="39" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B22" s="39" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C22" s="39">
         <v>4</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="E22" s="39" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F22" s="39" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="G22" s="39" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H22" s="39" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I22" s="39" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="J22" s="39" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K22" s="39">
         <v>6</v>
@@ -8060,34 +8273,34 @@
     </row>
     <row r="23" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="15" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C23" s="27">
         <v>4</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F23" s="51" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I23" s="27" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="J23" s="27" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="K23" s="16">
         <v>7</v>
@@ -8109,34 +8322,34 @@
     </row>
     <row r="24" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="39" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B24" s="39" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C24" s="39">
         <v>4</v>
       </c>
       <c r="D24" s="39" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="E24" s="39" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F24" s="39" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="G24" s="39" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H24" s="39" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I24" s="39" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="J24" s="39" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="K24" s="39">
         <v>8</v>
@@ -8158,34 +8371,34 @@
     </row>
     <row r="25" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C25" s="27">
         <v>4</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E25" s="27" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="F25" s="51" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I25" s="16" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="J25" s="16" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="K25" s="16">
         <v>8</v>
@@ -8207,34 +8420,34 @@
     </row>
     <row r="26" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="41" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B26" s="41" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C26" s="41">
         <v>5</v>
       </c>
       <c r="D26" s="41" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E26" s="41" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F26" s="41" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="G26" s="41" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H26" s="41" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I26" s="41" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="J26" s="41" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="K26" s="41">
         <v>9</v>
@@ -8256,34 +8469,34 @@
     </row>
     <row r="27" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="15" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C27" s="27">
         <v>5</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E27" s="27" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="F27" s="51" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="G27" s="27" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I27" s="27" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="J27" s="16" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="K27" s="16">
         <v>9</v>
@@ -8305,34 +8518,34 @@
     </row>
     <row r="28" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="41" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B28" s="41" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C28" s="41">
         <v>5</v>
       </c>
       <c r="D28" s="41" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E28" s="41" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F28" s="41" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="G28" s="68" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="H28" s="41" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I28" s="41" t="s">
         <v>11</v>
       </c>
       <c r="J28" s="41" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="K28" s="41">
         <v>10</v>
@@ -8354,34 +8567,34 @@
     </row>
     <row r="29" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="15" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C29" s="27">
         <v>5</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E29" s="27" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F29" s="51" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I29" s="16" t="s">
         <v>11</v>
       </c>
       <c r="J29" s="27" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="K29" s="16">
         <v>11</v>
@@ -8403,34 +8616,34 @@
     </row>
     <row r="30" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="41" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B30" s="41" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C30" s="41">
         <v>5</v>
       </c>
       <c r="D30" s="41" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E30" s="41" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F30" s="41" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="G30" s="68" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="H30" s="41" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I30" s="41" t="s">
         <v>11</v>
       </c>
       <c r="J30" s="41" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="K30" s="41">
         <v>12</v>
@@ -8452,34 +8665,34 @@
     </row>
     <row r="31" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="15" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C31" s="27">
         <v>5</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="F31" s="51" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I31" s="16" t="s">
         <v>11</v>
       </c>
       <c r="J31" s="27" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="K31" s="16">
         <v>12</v>

--- a/Src/Assets/Common/Tables/Tables/Levels.xlsx
+++ b/Src/Assets/Common/Tables/Tables/Levels.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CCA\Src\Assets\Common\Tables\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6867075D-A563-474B-A0D9-C92C654A91BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4038F88-340B-493E-8C04-90F59B3F7BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Character" sheetId="2" r:id="rId1"/>
@@ -1362,10 +1362,6 @@
   </si>
   <si>
     <t>[]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>["Save Me!!!"]</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -1980,6 +1976,32 @@
   <si>
     <t>PreviousLevel</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>["Save</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> Me"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2297,7 +2319,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2467,9 +2489,6 @@
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3207,13 +3226,13 @@
         <v>2</v>
       </c>
       <c r="E1" s="36" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F1" s="22" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="36" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1" s="22" t="s">
         <v>8</v>
@@ -3278,7 +3297,7 @@
         <v>250</v>
       </c>
       <c r="M2" s="26" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N2" s="26" t="s">
         <v>359</v>
@@ -3324,7 +3343,7 @@
         <v>12</v>
       </c>
       <c r="M3" s="16" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N3" s="11" t="s">
         <v>359</v>
@@ -3368,7 +3387,7 @@
         <v>12</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N4" s="7" t="s">
         <v>359</v>
@@ -3414,7 +3433,7 @@
         <v>12</v>
       </c>
       <c r="M5" s="16" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N5" s="11" t="s">
         <v>359</v>
@@ -3437,7 +3456,7 @@
       <c r="E6" s="26" t="s">
         <v>233</v>
       </c>
-      <c r="F6" s="61" t="b">
+      <c r="F6" s="60" t="b">
         <v>1</v>
       </c>
       <c r="G6" s="6"/>
@@ -3458,10 +3477,10 @@
         <v>12</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>421</v>
-      </c>
-      <c r="N6" s="58" t="s">
-        <v>360</v>
+        <v>420</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>489</v>
       </c>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
@@ -3488,7 +3507,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="29" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I7" s="11" t="s">
         <v>11</v>
@@ -3504,10 +3523,10 @@
         <v>12</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N7" s="29" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3548,10 +3567,10 @@
         <v>250</v>
       </c>
       <c r="M8" s="33" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N8" s="33" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="O8" s="33"/>
       <c r="P8" s="33"/>
@@ -3595,7 +3614,7 @@
         <v>12</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N9" s="11" t="s">
         <v>359</v>
@@ -3639,7 +3658,7 @@
         <v>12</v>
       </c>
       <c r="M10" s="32" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N10" s="32" t="s">
         <v>359</v>
@@ -3686,7 +3705,7 @@
         <v>12</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N11" s="11" t="s">
         <v>359</v>
@@ -3730,7 +3749,7 @@
         <v>12</v>
       </c>
       <c r="M12" s="32" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N12" s="32" t="s">
         <v>359</v>
@@ -3779,10 +3798,10 @@
         <v>12</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N13" s="29" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3823,10 +3842,10 @@
         <v>250</v>
       </c>
       <c r="M14" s="33" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N14" s="33" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="O14" s="33"/>
       <c r="P14" s="33"/>
@@ -3872,10 +3891,10 @@
         <v>246</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N15" s="29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3918,10 +3937,10 @@
         <v>12</v>
       </c>
       <c r="M16" s="32" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N16" s="33" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="O16" s="32"/>
       <c r="P16" s="32"/>
@@ -3967,10 +3986,10 @@
         <v>12</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N17" s="29" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4006,10 +4025,10 @@
         <v>12</v>
       </c>
       <c r="M18" s="32" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N18" s="33" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O18" s="32"/>
       <c r="P18" s="32"/>
@@ -4053,7 +4072,7 @@
         <v>12</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N19" s="11" t="s">
         <v>359</v>
@@ -4094,13 +4113,13 @@
         <v>2</v>
       </c>
       <c r="L20" s="33" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M20" s="32" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N20" s="33" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="O20" s="32"/>
       <c r="P20" s="32"/>
@@ -4127,7 +4146,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H21" s="11" t="s">
         <v>11</v>
@@ -4146,10 +4165,10 @@
         <v>357</v>
       </c>
       <c r="M21" s="16" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N21" s="29" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4192,10 +4211,10 @@
         <v>12</v>
       </c>
       <c r="M22" s="34" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N22" s="53" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="O22" s="34"/>
       <c r="P22" s="34"/>
@@ -4241,10 +4260,10 @@
         <v>250</v>
       </c>
       <c r="M23" s="29" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N23" s="29" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O23" s="29"/>
       <c r="P23" s="29"/>
@@ -4290,7 +4309,7 @@
         <v>250</v>
       </c>
       <c r="M24" s="34" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N24" s="34" t="s">
         <v>359</v>
@@ -4337,10 +4356,10 @@
         <v>250</v>
       </c>
       <c r="M25" s="29" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N25" s="29" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="O25" s="29"/>
       <c r="P25" s="29"/>
@@ -4384,7 +4403,7 @@
         <v>12</v>
       </c>
       <c r="M26" s="34" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N26" s="34" t="s">
         <v>359</v>
@@ -4431,10 +4450,10 @@
         <v>250</v>
       </c>
       <c r="M27" s="29" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N27" s="29" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="O27" s="29"/>
       <c r="P27" s="29"/>
@@ -4480,7 +4499,7 @@
         <v>12</v>
       </c>
       <c r="M28" s="34" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N28" s="34" t="s">
         <v>359</v>
@@ -4529,7 +4548,7 @@
         <v>250</v>
       </c>
       <c r="M29" s="29" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N29" s="29" t="s">
         <v>359</v>
@@ -4578,7 +4597,7 @@
         <v>250</v>
       </c>
       <c r="M30" s="34" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N30" s="34" t="s">
         <v>359</v>
@@ -4625,10 +4644,10 @@
         <v>250</v>
       </c>
       <c r="M31" s="29" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N31" s="29" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="O31" s="29"/>
       <c r="P31" s="29"/>
@@ -4655,7 +4674,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="53" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H32" s="34" t="s">
         <v>11</v>
@@ -4674,10 +4693,10 @@
         <v>250</v>
       </c>
       <c r="M32" s="34" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N32" s="53" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O32" s="34"/>
       <c r="P32" s="34"/>
@@ -4704,7 +4723,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="29" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H33" s="29" t="s">
         <v>11</v>
@@ -4723,10 +4742,10 @@
         <v>250</v>
       </c>
       <c r="M33" s="29" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N33" s="29" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="O33" s="29"/>
       <c r="P33" s="29"/>
@@ -4753,7 +4772,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="34" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H34" s="34" t="s">
         <v>11</v>
@@ -4772,10 +4791,10 @@
         <v>12</v>
       </c>
       <c r="M34" s="34" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N34" s="53" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="O34" s="34"/>
       <c r="P34" s="34"/>
@@ -4821,10 +4840,10 @@
         <v>250</v>
       </c>
       <c r="M35" s="29" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N35" s="29" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="O35" s="29"/>
       <c r="P35" s="29"/>
@@ -4868,10 +4887,10 @@
         <v>250</v>
       </c>
       <c r="M36" s="34" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N36" s="53" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="O36" s="34"/>
       <c r="P36" s="34"/>
@@ -4915,10 +4934,10 @@
         <v>250</v>
       </c>
       <c r="M37" s="29" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N37" s="29" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="O37" s="29"/>
       <c r="P37" s="29"/>
@@ -4962,10 +4981,10 @@
         <v>250</v>
       </c>
       <c r="M38" s="37" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N38" s="37" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="O38" s="37"/>
       <c r="P38" s="37"/>
@@ -5011,7 +5030,7 @@
         <v>12</v>
       </c>
       <c r="M39" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N39" s="29" t="s">
         <v>359</v>
@@ -5055,10 +5074,10 @@
         <v>250</v>
       </c>
       <c r="M40" s="39" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N40" s="39" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="O40" s="39"/>
       <c r="P40" s="39"/>
@@ -5104,10 +5123,10 @@
         <v>250</v>
       </c>
       <c r="M41" s="38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N41" s="38" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="O41" s="38"/>
       <c r="P41" s="38"/>
@@ -5153,10 +5172,10 @@
         <v>250</v>
       </c>
       <c r="M42" s="39" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N42" s="39" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="O42" s="39"/>
       <c r="P42" s="39"/>
@@ -5199,13 +5218,13 @@
         <v>2</v>
       </c>
       <c r="L43" s="38" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M43" s="38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N43" s="38" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="O43" s="38"/>
       <c r="P43" s="38"/>
@@ -5235,7 +5254,7 @@
         <v>242</v>
       </c>
       <c r="H44" s="39" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="I44" s="39" t="s">
         <v>11</v>
@@ -5251,10 +5270,10 @@
         <v>250</v>
       </c>
       <c r="M44" s="39" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N44" s="39" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="O44" s="39"/>
       <c r="P44" s="39"/>
@@ -5297,13 +5316,13 @@
         <v>3</v>
       </c>
       <c r="L45" s="38" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="M45" s="38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N45" s="38" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="O45" s="38"/>
       <c r="P45" s="38"/>
@@ -5349,10 +5368,10 @@
         <v>250</v>
       </c>
       <c r="M46" s="39" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N46" s="39" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="O46" s="39"/>
       <c r="P46" s="39"/>
@@ -5398,10 +5417,10 @@
         <v>250</v>
       </c>
       <c r="M47" s="38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N47" s="38" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="O47" s="38"/>
       <c r="P47" s="38"/>
@@ -5447,10 +5466,10 @@
         <v>250</v>
       </c>
       <c r="M48" s="39" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N48" s="39" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O48" s="39"/>
       <c r="P48" s="39"/>
@@ -5496,10 +5515,10 @@
         <v>250</v>
       </c>
       <c r="M49" s="38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N49" s="38" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="O49" s="38"/>
       <c r="P49" s="38"/>
@@ -5545,10 +5564,10 @@
         <v>250</v>
       </c>
       <c r="M50" s="39" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N50" s="39" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="O50" s="39"/>
       <c r="P50" s="39"/>
@@ -5592,10 +5611,10 @@
         <v>250</v>
       </c>
       <c r="M51" s="38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N51" s="38" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="O51" s="38"/>
       <c r="P51" s="38"/>
@@ -5637,10 +5656,10 @@
         <v>250</v>
       </c>
       <c r="M52" s="39" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N52" s="39" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="O52" s="39"/>
       <c r="P52" s="39"/>
@@ -5682,10 +5701,10 @@
         <v>250</v>
       </c>
       <c r="M53" s="38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N53" s="38" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="O53" s="38"/>
       <c r="P53" s="38"/>
@@ -5729,10 +5748,10 @@
         <v>250</v>
       </c>
       <c r="M54" s="39" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N54" s="39" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="O54" s="39"/>
       <c r="P54" s="39"/>
@@ -5776,10 +5795,10 @@
         <v>250</v>
       </c>
       <c r="M55" s="38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N55" s="38" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="O55" s="38"/>
       <c r="P55" s="38"/>
@@ -5822,13 +5841,13 @@
         <v>8</v>
       </c>
       <c r="L56" s="39" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="M56" s="39" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N56" s="39" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O56" s="39"/>
       <c r="P56" s="39"/>
@@ -5874,10 +5893,10 @@
         <v>250</v>
       </c>
       <c r="M57" s="38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N57" s="38" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O57" s="38"/>
       <c r="P57" s="38"/>
@@ -5923,10 +5942,10 @@
         <v>250</v>
       </c>
       <c r="M58" s="39" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N58" s="39" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O58" s="39"/>
       <c r="P58" s="39"/>
@@ -5964,10 +5983,10 @@
         <v>12</v>
       </c>
       <c r="M59" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N59" s="29" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="60" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6004,10 +6023,10 @@
         <v>250</v>
       </c>
       <c r="M60" s="41" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N60" s="41" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="O60" s="41"/>
       <c r="P60" s="41"/>
@@ -6049,10 +6068,10 @@
         <v>250</v>
       </c>
       <c r="M61" s="38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N61" s="38" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O61" s="38"/>
       <c r="P61" s="38"/>
@@ -6094,10 +6113,10 @@
         <v>250</v>
       </c>
       <c r="M62" s="41" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N62" s="41" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="O62" s="41"/>
       <c r="P62" s="41"/>
@@ -6137,10 +6156,10 @@
         <v>250</v>
       </c>
       <c r="M63" s="38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N63" s="38" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="O63" s="38"/>
       <c r="P63" s="38"/>
@@ -6180,10 +6199,10 @@
         <v>250</v>
       </c>
       <c r="M64" s="41" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N64" s="41" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="O64" s="41"/>
       <c r="P64" s="41"/>
@@ -6223,10 +6242,10 @@
         <v>250</v>
       </c>
       <c r="M65" s="38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N65" s="38" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="O65" s="38"/>
       <c r="P65" s="38"/>
@@ -6266,10 +6285,10 @@
         <v>250</v>
       </c>
       <c r="M66" s="41" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N66" s="41" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="O66" s="41"/>
       <c r="P66" s="41"/>
@@ -6309,10 +6328,10 @@
         <v>250</v>
       </c>
       <c r="M67" s="38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N67" s="38" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="O67" s="38"/>
       <c r="P67" s="38"/>
@@ -6352,10 +6371,10 @@
         <v>250</v>
       </c>
       <c r="M68" s="41" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N68" s="41" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="O68" s="41"/>
       <c r="P68" s="41"/>
@@ -6395,10 +6414,10 @@
         <v>250</v>
       </c>
       <c r="M69" s="38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N69" s="38" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="O69" s="38"/>
       <c r="P69" s="38"/>
@@ -6438,10 +6457,10 @@
         <v>250</v>
       </c>
       <c r="M70" s="41" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N70" s="41" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="O70" s="41"/>
       <c r="P70" s="41"/>
@@ -6483,10 +6502,10 @@
         <v>250</v>
       </c>
       <c r="M71" s="38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N71" s="38" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="O71" s="38"/>
       <c r="P71" s="38"/>
@@ -6526,10 +6545,10 @@
         <v>250</v>
       </c>
       <c r="M72" s="41" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N72" s="41" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="O72" s="41"/>
       <c r="P72" s="41"/>
@@ -6571,10 +6590,10 @@
         <v>250</v>
       </c>
       <c r="M73" s="38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N73" s="38" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="O73" s="38"/>
       <c r="P73" s="38"/>
@@ -6618,10 +6637,10 @@
         <v>250</v>
       </c>
       <c r="M74" s="41" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N74" s="41" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="O74" s="41"/>
       <c r="P74" s="41"/>
@@ -6665,10 +6684,10 @@
         <v>250</v>
       </c>
       <c r="M75" s="38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N75" s="38" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="O75" s="38"/>
       <c r="P75" s="38"/>
@@ -6707,13 +6726,13 @@
         <v>13</v>
       </c>
       <c r="L76" s="41" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="M76" s="41" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N76" s="41" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="O76" s="41"/>
       <c r="P76" s="41"/>
@@ -6753,10 +6772,10 @@
         <v>250</v>
       </c>
       <c r="M77" s="38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N77" s="38" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="O77" s="38"/>
       <c r="P77" s="38"/>
@@ -6798,10 +6817,10 @@
         <v>250</v>
       </c>
       <c r="M78" s="41" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N78" s="41" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O78" s="41"/>
       <c r="P78" s="41"/>
@@ -6841,10 +6860,10 @@
         <v>250</v>
       </c>
       <c r="M79" s="38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N79" s="38" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="O79" s="38"/>
       <c r="P79" s="38"/>
@@ -6884,10 +6903,10 @@
         <v>250</v>
       </c>
       <c r="M80" s="41" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N80" s="41" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="O80" s="41"/>
       <c r="P80" s="41"/>
@@ -6924,13 +6943,13 @@
         <v>28</v>
       </c>
       <c r="L81" s="38" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="M81" s="38" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N81" s="38" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="O81" s="38"/>
       <c r="P81" s="38"/>
@@ -6938,14 +6957,14 @@
     </row>
     <row r="82" spans="1:17" ht="13.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="41" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B82" s="41" t="str">
         <f>A82</f>
         <v>Counter-Blade</v>
       </c>
       <c r="C82" s="41" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D82" s="41" t="s">
         <v>228</v>
@@ -6972,10 +6991,10 @@
         <v>250</v>
       </c>
       <c r="M82" s="41" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N82" s="41" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="O82" s="41"/>
       <c r="P82" s="41"/>
@@ -7227,7 +7246,7 @@
         <v>30</v>
       </c>
       <c r="J1" s="56" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>31</v>
@@ -7239,10 +7258,10 @@
         <v>33</v>
       </c>
       <c r="N1" s="22" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O1" s="22" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -7271,7 +7290,7 @@
         <v>317</v>
       </c>
       <c r="I2" s="26" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J2" s="26" t="s">
         <v>317</v>
@@ -7285,7 +7304,7 @@
       <c r="M2" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="59"/>
+      <c r="N2" s="58"/>
       <c r="O2" s="6" t="str">
         <f t="shared" ref="O2:O30" si="0">A3</f>
         <v>1-2</v>
@@ -7317,10 +7336,10 @@
         <v>317</v>
       </c>
       <c r="I3" s="27" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J3" s="27" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="K3" s="16">
         <v>0</v>
@@ -7366,7 +7385,7 @@
         <v>317</v>
       </c>
       <c r="I4" s="26" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J4" s="6" t="s">
         <v>317</v>
@@ -7409,13 +7428,13 @@
         <v>308</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H5" s="16" t="s">
         <v>317</v>
       </c>
       <c r="I5" s="27" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="J5" s="16" t="s">
         <v>317</v>
@@ -7467,7 +7486,7 @@
         <v>11</v>
       </c>
       <c r="J6" s="26" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="K6" s="6">
         <v>1</v>
@@ -7476,7 +7495,7 @@
         <v>4</v>
       </c>
       <c r="M6" s="25" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="N6" s="6" t="str">
         <f t="shared" si="1"/>
@@ -7510,13 +7529,13 @@
         <v>317</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="I7" s="27" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J7" s="27" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="K7" s="16">
         <v>1</v>
@@ -7559,22 +7578,22 @@
         <v>317</v>
       </c>
       <c r="H8" s="52" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="I8" s="52" t="s">
         <v>43</v>
       </c>
       <c r="J8" s="52" t="s">
-        <v>445</v>
-      </c>
-      <c r="K8" s="62">
+        <v>444</v>
+      </c>
+      <c r="K8" s="61">
         <v>1</v>
       </c>
-      <c r="L8" s="62">
+      <c r="L8" s="61">
         <v>5</v>
       </c>
       <c r="M8" s="52" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="N8" s="52" t="str">
         <f t="shared" si="1"/>
@@ -7611,10 +7630,10 @@
         <v>317</v>
       </c>
       <c r="I9" s="57" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J9" s="57" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="K9" s="27">
         <v>2</v>
@@ -7653,22 +7672,22 @@
       <c r="F10" s="52" t="s">
         <v>313</v>
       </c>
-      <c r="G10" s="67" t="s">
-        <v>484</v>
+      <c r="G10" s="66" t="s">
+        <v>483</v>
       </c>
       <c r="H10" s="52" t="s">
         <v>317</v>
       </c>
       <c r="I10" s="52" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="J10" s="52" t="s">
         <v>317</v>
       </c>
-      <c r="K10" s="62">
+      <c r="K10" s="61">
         <v>2</v>
       </c>
-      <c r="L10" s="62">
+      <c r="L10" s="61">
         <v>6</v>
       </c>
       <c r="M10" s="52" t="s">
@@ -7709,10 +7728,10 @@
         <v>317</v>
       </c>
       <c r="I11" s="57" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="K11" s="27">
         <v>3</v>
@@ -7758,15 +7777,15 @@
         <v>317</v>
       </c>
       <c r="I12" s="52" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="J12" s="52" t="s">
-        <v>447</v>
-      </c>
-      <c r="K12" s="62">
+        <v>446</v>
+      </c>
+      <c r="K12" s="61">
         <v>3</v>
       </c>
-      <c r="L12" s="62">
+      <c r="L12" s="61">
         <v>7</v>
       </c>
       <c r="M12" s="52" t="s">
@@ -7807,10 +7826,10 @@
         <v>317</v>
       </c>
       <c r="I13" s="27" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="J13" s="27" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="K13" s="16">
         <v>3</v>
@@ -7818,7 +7837,7 @@
       <c r="L13" s="51">
         <v>7</v>
       </c>
-      <c r="M13" s="63" t="s">
+      <c r="M13" s="62" t="s">
         <v>12</v>
       </c>
       <c r="N13" s="9" t="str">
@@ -7856,10 +7875,10 @@
         <v>317</v>
       </c>
       <c r="I14" s="33" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="J14" s="33" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="K14" s="33">
         <v>4</v>
@@ -7867,7 +7886,7 @@
       <c r="L14" s="33">
         <v>7</v>
       </c>
-      <c r="M14" s="64" t="s">
+      <c r="M14" s="63" t="s">
         <v>12</v>
       </c>
       <c r="N14" s="33" t="str">
@@ -7905,10 +7924,10 @@
         <v>317</v>
       </c>
       <c r="I15" s="27" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="K15" s="16">
         <v>4</v>
@@ -7957,7 +7976,7 @@
         <v>11</v>
       </c>
       <c r="J16" s="33" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="K16" s="33">
         <v>5</v>
@@ -7965,7 +7984,7 @@
       <c r="L16" s="33">
         <v>8</v>
       </c>
-      <c r="M16" s="64" t="s">
+      <c r="M16" s="63" t="s">
         <v>12</v>
       </c>
       <c r="N16" s="33" t="str">
@@ -8003,10 +8022,10 @@
         <v>317</v>
       </c>
       <c r="I17" s="27" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="J17" s="27" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K17" s="16">
         <v>5</v>
@@ -8052,10 +8071,10 @@
         <v>317</v>
       </c>
       <c r="I18" s="33" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="J18" s="33" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K18" s="33">
         <v>5</v>
@@ -8063,7 +8082,7 @@
       <c r="L18" s="33">
         <v>9</v>
       </c>
-      <c r="M18" s="64" t="s">
+      <c r="M18" s="63" t="s">
         <v>12</v>
       </c>
       <c r="N18" s="33" t="str">
@@ -8104,7 +8123,7 @@
         <v>317</v>
       </c>
       <c r="J19" s="27" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K19" s="16">
         <v>6</v>
@@ -8150,10 +8169,10 @@
         <v>317</v>
       </c>
       <c r="I20" s="39" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="J20" s="39" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K20" s="39">
         <v>6</v>
@@ -8161,7 +8180,7 @@
       <c r="L20" s="39">
         <v>10</v>
       </c>
-      <c r="M20" s="65" t="s">
+      <c r="M20" s="64" t="s">
         <v>12</v>
       </c>
       <c r="N20" s="39" t="str">
@@ -8199,7 +8218,7 @@
         <v>317</v>
       </c>
       <c r="I21" s="27" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="J21" s="16" t="s">
         <v>317</v>
@@ -8210,7 +8229,7 @@
       <c r="L21" s="51">
         <v>10</v>
       </c>
-      <c r="M21" s="63" t="s">
+      <c r="M21" s="62" t="s">
         <v>12</v>
       </c>
       <c r="N21" s="9" t="str">
@@ -8248,10 +8267,10 @@
         <v>317</v>
       </c>
       <c r="I22" s="39" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="J22" s="39" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="K22" s="39">
         <v>6</v>
@@ -8259,7 +8278,7 @@
       <c r="L22" s="39">
         <v>11</v>
       </c>
-      <c r="M22" s="65" t="s">
+      <c r="M22" s="64" t="s">
         <v>12</v>
       </c>
       <c r="N22" s="39" t="str">
@@ -8300,7 +8319,7 @@
         <v>317</v>
       </c>
       <c r="J23" s="27" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K23" s="16">
         <v>7</v>
@@ -8308,7 +8327,7 @@
       <c r="L23" s="51">
         <v>12</v>
       </c>
-      <c r="M23" s="63" t="s">
+      <c r="M23" s="62" t="s">
         <v>12</v>
       </c>
       <c r="N23" s="9" t="str">
@@ -8349,7 +8368,7 @@
         <v>317</v>
       </c>
       <c r="J24" s="39" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K24" s="39">
         <v>8</v>
@@ -8357,7 +8376,7 @@
       <c r="L24" s="39">
         <v>12</v>
       </c>
-      <c r="M24" s="65" t="s">
+      <c r="M24" s="64" t="s">
         <v>12</v>
       </c>
       <c r="N24" s="39" t="str">
@@ -8406,7 +8425,7 @@
       <c r="L25" s="51">
         <v>12</v>
       </c>
-      <c r="M25" s="63" t="s">
+      <c r="M25" s="62" t="s">
         <v>12</v>
       </c>
       <c r="N25" s="9" t="str">
@@ -8447,7 +8466,7 @@
         <v>317</v>
       </c>
       <c r="J26" s="41" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="K26" s="41">
         <v>9</v>
@@ -8455,7 +8474,7 @@
       <c r="L26" s="41">
         <v>13</v>
       </c>
-      <c r="M26" s="66" t="s">
+      <c r="M26" s="65" t="s">
         <v>12</v>
       </c>
       <c r="N26" s="41" t="str">
@@ -8493,7 +8512,7 @@
         <v>317</v>
       </c>
       <c r="I27" s="27" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="J27" s="16" t="s">
         <v>317</v>
@@ -8535,8 +8554,8 @@
       <c r="F28" s="41" t="s">
         <v>348</v>
       </c>
-      <c r="G28" s="68" t="s">
-        <v>485</v>
+      <c r="G28" s="67" t="s">
+        <v>484</v>
       </c>
       <c r="H28" s="41" t="s">
         <v>317</v>
@@ -8545,7 +8564,7 @@
         <v>11</v>
       </c>
       <c r="J28" s="41" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K28" s="41">
         <v>10</v>
@@ -8553,7 +8572,7 @@
       <c r="L28" s="41">
         <v>14</v>
       </c>
-      <c r="M28" s="66" t="s">
+      <c r="M28" s="65" t="s">
         <v>12</v>
       </c>
       <c r="N28" s="41" t="str">
@@ -8585,7 +8604,7 @@
         <v>349</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H29" s="16" t="s">
         <v>317</v>
@@ -8594,7 +8613,7 @@
         <v>11</v>
       </c>
       <c r="J29" s="27" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="K29" s="16">
         <v>11</v>
@@ -8633,8 +8652,8 @@
       <c r="F30" s="41" t="s">
         <v>350</v>
       </c>
-      <c r="G30" s="68" t="s">
-        <v>485</v>
+      <c r="G30" s="67" t="s">
+        <v>484</v>
       </c>
       <c r="H30" s="41" t="s">
         <v>317</v>
@@ -8643,7 +8662,7 @@
         <v>11</v>
       </c>
       <c r="J30" s="41" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K30" s="41">
         <v>12</v>
@@ -8651,7 +8670,7 @@
       <c r="L30" s="41">
         <v>14</v>
       </c>
-      <c r="M30" s="66" t="s">
+      <c r="M30" s="65" t="s">
         <v>12</v>
       </c>
       <c r="N30" s="41" t="str">
@@ -8683,7 +8702,7 @@
         <v>351</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H31" s="16" t="s">
         <v>317</v>
@@ -8692,7 +8711,7 @@
         <v>11</v>
       </c>
       <c r="J31" s="27" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="K31" s="16">
         <v>12</v>
@@ -8707,7 +8726,7 @@
         <f t="shared" si="1"/>
         <v>5-5</v>
       </c>
-      <c r="O31" s="60"/>
+      <c r="O31" s="59"/>
     </row>
     <row r="32" spans="1:15" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="25"/>
